--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>7.27</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>7.27</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>7.27</v>
+        <v>3.24</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P23" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P4" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="P5" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>7.27</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.57</v>
+        <v>3.74</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>2.87</v>
       </c>
       <c r="O8" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>3.74</v>
+        <v>2.41</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P16" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>4.95</v>
+        <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>7.27</v>
+        <v>3.63</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P23" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>2.56</v>
       </c>
       <c r="O33" t="n">
-        <v>5.25</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>5.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.91</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
-        <v>7.27</v>
+        <v>3.24</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.91</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.57</v>
+        <v>3.74</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>4.95</v>
       </c>
       <c r="P16" t="n">
-        <v>3.24</v>
+        <v>7.27</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>7.27</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>3.74</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="O5" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.03</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>3.74</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>7.27</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>7.27</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="P4" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.87</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>3.74</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P8" t="n">
         <v>3.05</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.57</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.76</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>3.63</v>
+        <v>3.24</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>7.27</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>4.95</v>
+        <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>7.27</v>
+        <v>3.63</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P23" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>2.56</v>
       </c>
       <c r="O33" t="n">
-        <v>5.25</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>5.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>3.54</v>
+        <v>3.26</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.03</v>
+        <v>2.87</v>
       </c>
       <c r="O7" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>3.74</v>
+        <v>2.41</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>3.76</v>
       </c>
       <c r="P15" t="n">
-        <v>3.24</v>
+        <v>3.63</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
-        <v>7.27</v>
+        <v>3.24</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="P4" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="P7" t="n">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>2.87</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.38</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>4.28</v>
+        <v>3.76</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>3.63</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.76</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>3.63</v>
+        <v>3.24</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>4.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>4.28</v>
       </c>
       <c r="P16" t="n">
-        <v>3.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.89</v>
+        <v>1.37</v>
       </c>
       <c r="O26" t="n">
-        <v>3.83</v>
+        <v>5.06</v>
       </c>
       <c r="P26" t="n">
-        <v>3.91</v>
+        <v>8.25</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>5.06</v>
+        <v>3.83</v>
       </c>
       <c r="P27" t="n">
-        <v>8.25</v>
+        <v>3.91</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.54</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.57</v>
+        <v>3.74</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.03</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>3.74</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>4.38</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>4.28</v>
       </c>
       <c r="P15" t="n">
-        <v>3.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.38</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>4.28</v>
+        <v>4.95</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>7.27</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O17" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="P17" t="n">
-        <v>7.27</v>
+        <v>3.24</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.19</v>
+        <v>2.56</v>
       </c>
       <c r="O33" t="n">
-        <v>6.35</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>8.050000000000001</v>
+        <v>2.36</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="O34" t="n">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="P34" t="n">
-        <v>5.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="P5" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O14" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P14" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>4.95</v>
+        <v>3.76</v>
       </c>
       <c r="P16" t="n">
-        <v>7.27</v>
+        <v>3.63</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="O25" t="n">
-        <v>4.05</v>
+        <v>5.06</v>
       </c>
       <c r="P25" t="n">
-        <v>5.12</v>
+        <v>8.25</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="O26" t="n">
-        <v>5.06</v>
+        <v>4.05</v>
       </c>
       <c r="P26" t="n">
-        <v>8.25</v>
+        <v>5.12</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.19</v>
+        <v>2.56</v>
       </c>
       <c r="O34" t="n">
-        <v>6.35</v>
+        <v>3.78</v>
       </c>
       <c r="P34" t="n">
-        <v>8.050000000000001</v>
+        <v>2.36</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="O35" t="n">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="P35" t="n">
-        <v>5.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.41</v>
+        <v>3.74</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.03</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.74</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="P14" t="n">
-        <v>7.27</v>
+        <v>3.24</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P16" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.54</v>
+        <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>3.24</v>
+        <v>3.63</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>5.06</v>
+        <v>3.83</v>
       </c>
       <c r="P25" t="n">
-        <v>8.25</v>
+        <v>3.91</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="O26" t="n">
-        <v>4.05</v>
+        <v>5.06</v>
       </c>
       <c r="P26" t="n">
-        <v>5.12</v>
+        <v>8.25</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="O27" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="P27" t="n">
-        <v>3.91</v>
+        <v>5.12</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="O33" t="n">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="P33" t="n">
-        <v>5.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.19</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
-        <v>6.35</v>
+        <v>3.78</v>
       </c>
       <c r="P35" t="n">
-        <v>8.050000000000001</v>
+        <v>2.36</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8549,10 +8549,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>2.41</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>4.38</v>
       </c>
       <c r="O14" t="n">
-        <v>3.54</v>
+        <v>4.28</v>
       </c>
       <c r="P14" t="n">
-        <v>3.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.38</v>
+        <v>1.37</v>
       </c>
       <c r="O15" t="n">
-        <v>4.28</v>
+        <v>4.95</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>7.27</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
-        <v>7.27</v>
+        <v>3.24</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P23" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="O25" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>3.91</v>
+        <v>5.12</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>4.05</v>
+        <v>3.83</v>
       </c>
       <c r="P27" t="n">
-        <v>5.12</v>
+        <v>3.91</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.19</v>
+        <v>2.56</v>
       </c>
       <c r="O33" t="n">
-        <v>6.35</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>8.050000000000001</v>
+        <v>2.36</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>1.19</v>
       </c>
       <c r="O35" t="n">
-        <v>3.78</v>
+        <v>6.35</v>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="O48" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="P48" t="n">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="O49" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="P49" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O51" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8549,16 +8549,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="P7" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.38</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>4.28</v>
+        <v>3.76</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>3.63</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>7.27</v>
+        <v>3.24</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>4.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>4.28</v>
       </c>
       <c r="P16" t="n">
-        <v>3.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>4.05</v>
+        <v>3.83</v>
       </c>
       <c r="P25" t="n">
-        <v>5.12</v>
+        <v>3.91</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="O26" t="n">
-        <v>5.06</v>
+        <v>4.05</v>
       </c>
       <c r="P26" t="n">
-        <v>8.25</v>
+        <v>5.12</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>1.37</v>
       </c>
       <c r="O27" t="n">
-        <v>3.83</v>
+        <v>5.06</v>
       </c>
       <c r="P27" t="n">
-        <v>3.91</v>
+        <v>8.25</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="O48" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="P48" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="O49" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="P49" t="n">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8549,16 +8549,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="O53" t="n">
-        <v>3.72</v>
+        <v>2.86</v>
       </c>
       <c r="P53" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O14" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P14" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>3.76</v>
       </c>
       <c r="P15" t="n">
-        <v>3.24</v>
+        <v>3.63</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.38</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>4.28</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>3.24</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>4.38</v>
       </c>
       <c r="O17" t="n">
-        <v>4.95</v>
+        <v>4.28</v>
       </c>
       <c r="P17" t="n">
-        <v>7.27</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="O25" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>3.91</v>
+        <v>5.12</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="O26" t="n">
-        <v>4.05</v>
+        <v>5.06</v>
       </c>
       <c r="P26" t="n">
-        <v>5.12</v>
+        <v>8.25</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>5.06</v>
+        <v>3.83</v>
       </c>
       <c r="P27" t="n">
-        <v>8.25</v>
+        <v>3.91</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O51" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8549,16 +8549,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="O53" t="n">
-        <v>2.86</v>
+        <v>3.72</v>
       </c>
       <c r="P53" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="O55" t="n">
-        <v>3.72</v>
+        <v>2.86</v>
       </c>
       <c r="P55" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="P4" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="O5" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>3.26</v>
       </c>
       <c r="P8" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.76</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>3.63</v>
+        <v>3.24</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>3.76</v>
       </c>
       <c r="P16" t="n">
-        <v>3.24</v>
+        <v>3.63</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3119,55 +3119,55 @@
         <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.81</v>
+        <v>3.13</v>
       </c>
       <c r="P22" t="n">
-        <v>3.01</v>
+        <v>3.14</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="O25" t="n">
-        <v>4.05</v>
+        <v>5.06</v>
       </c>
       <c r="P25" t="n">
-        <v>5.12</v>
+        <v>8.25</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="O26" t="n">
-        <v>5.06</v>
+        <v>3.83</v>
       </c>
       <c r="P26" t="n">
-        <v>8.25</v>
+        <v>3.91</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="O27" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="P27" t="n">
-        <v>3.91</v>
+        <v>5.12</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>2.56</v>
       </c>
       <c r="O34" t="n">
-        <v>5.25</v>
+        <v>3.78</v>
       </c>
       <c r="P34" t="n">
-        <v>5.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8549,16 +8549,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="O53" t="n">
-        <v>3.72</v>
+        <v>2.86</v>
       </c>
       <c r="P53" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="O55" t="n">
-        <v>2.86</v>
+        <v>3.72</v>
       </c>
       <c r="P55" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -734,55 +734,55 @@
         <v>3.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,65 +1202,65 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1370,55 +1370,55 @@
         <v>2.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>2.03</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2483,55 +2483,55 @@
         <v>3.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.37</v>
+        <v>4.38</v>
       </c>
       <c r="O14" t="n">
-        <v>4.95</v>
+        <v>4.28</v>
       </c>
       <c r="P14" t="n">
-        <v>7.27</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.1</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
-        <v>3.63</v>
+        <v>3.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.38</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>4.28</v>
+        <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>3.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>2.41</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
         <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
         <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3278,55 +3278,55 @@
         <v>1.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4073,55 +4073,55 @@
         <v>3.36</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4232,55 +4232,55 @@
         <v>1.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="O25" t="n">
-        <v>5.06</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>8.25</v>
+        <v>5.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4550,55 +4550,55 @@
         <v>3.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="P27" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.65</v>
       </c>
-      <c r="O27" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P27" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="O33" t="n">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="P33" t="n">
-        <v>5.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.19</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
-        <v>6.35</v>
+        <v>3.78</v>
       </c>
       <c r="P35" t="n">
-        <v>8.050000000000001</v>
+        <v>2.36</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="O53" t="n">
-        <v>2.86</v>
+        <v>3.72</v>
       </c>
       <c r="P53" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="O55" t="n">
-        <v>3.72</v>
+        <v>2.86</v>
       </c>
       <c r="P55" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S6" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="T6" t="n">
-        <v>2.69</v>
+        <v>2.34</v>
       </c>
       <c r="U6" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.33</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="O8" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>2.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="R8" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="U8" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.54</v>
+        <v>3.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="O19" t="n">
-        <v>3.13</v>
+        <v>2.81</v>
       </c>
       <c r="P19" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="Q19" t="n">
         <v>2.9</v>
@@ -3443,49 +3443,49 @@
         <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T19" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.05</v>
       </c>
       <c r="AF19" t="n">
         <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O25" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="P25" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.65</v>
       </c>
-      <c r="O25" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P25" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF25" t="n">
         <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="O26" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="P26" t="n">
-        <v>3.91</v>
+        <v>5.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="R26" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S26" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V26" t="n">
         <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>5.06</v>
+        <v>3.83</v>
       </c>
       <c r="P27" t="n">
-        <v>8.25</v>
+        <v>3.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.75</v>
+        <v>2.44</v>
       </c>
       <c r="R27" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.15</v>
+        <v>2.61</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK27" t="n">
-        <v>3.3</v>
+        <v>1.86</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="O33" t="n">
-        <v>6.35</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>8.050000000000001</v>
+        <v>5.32</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>2.56</v>
       </c>
       <c r="O34" t="n">
-        <v>5.25</v>
+        <v>3.78</v>
       </c>
       <c r="P34" t="n">
-        <v>5.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>1.19</v>
       </c>
       <c r="O35" t="n">
-        <v>3.78</v>
+        <v>6.35</v>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O51" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8549,16 +8549,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="O53" t="n">
-        <v>3.72</v>
+        <v>2.86</v>
       </c>
       <c r="P53" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="O55" t="n">
-        <v>2.86</v>
+        <v>3.72</v>
       </c>
       <c r="P55" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="O4" t="n">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,61 +1202,61 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
         <v>2.03</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T5" t="n">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.07</v>
+        <v>2.54</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
         <v>1.8</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,61 +1361,61 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="R6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.54</v>
+        <v>3.07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.6</v>
+        <v>3.76</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
         <v>1.8</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.38</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>4.28</v>
+        <v>3.76</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>3.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>2.41</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
         <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
         <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.37</v>
+        <v>4.38</v>
       </c>
       <c r="O15" t="n">
-        <v>4.95</v>
+        <v>4.28</v>
       </c>
       <c r="P15" t="n">
-        <v>7.27</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>3.55</v>
       </c>
       <c r="R15" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.85</v>
+        <v>4.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.63</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK15" t="n">
-        <v>2.75</v>
+        <v>1.38</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>2.81</v>
+        <v>3.13</v>
       </c>
       <c r="P19" t="n">
-        <v>3.01</v>
+        <v>3.14</v>
       </c>
       <c r="Q19" t="n">
         <v>2.9</v>
@@ -3443,49 +3443,49 @@
         <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U19" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
         <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P23" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.49</v>
+        <v>4.83</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="S23" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.77</v>
+        <v>3.55</v>
       </c>
       <c r="U23" t="n">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="V23" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.83</v>
+        <v>2.49</v>
       </c>
       <c r="R24" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T24" t="n">
-        <v>3.55</v>
+        <v>2.77</v>
       </c>
       <c r="U24" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="V24" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="O33" t="n">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="P33" t="n">
-        <v>5.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
-        <v>6.35</v>
+        <v>5.25</v>
       </c>
       <c r="P35" t="n">
-        <v>8.050000000000001</v>
+        <v>5.32</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6323,10 +6323,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6763,17 +6763,17 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8549,16 +8549,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,61 +1202,61 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="R5" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.54</v>
+        <v>3.07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.6</v>
+        <v>3.76</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG5" t="n">
         <v>1.8</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.54</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.38</v>
+        <v>1.37</v>
       </c>
       <c r="O15" t="n">
-        <v>4.28</v>
+        <v>4.95</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>7.27</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="S15" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.3</v>
+        <v>4.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.37</v>
+        <v>2.09</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.38</v>
+        <v>2.75</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>4.38</v>
       </c>
       <c r="O17" t="n">
-        <v>4.95</v>
+        <v>4.28</v>
       </c>
       <c r="P17" t="n">
-        <v>7.27</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.85</v>
+        <v>4.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.63</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK17" t="n">
-        <v>2.75</v>
+        <v>1.38</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="O25" t="n">
-        <v>5.06</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>8.25</v>
+        <v>5.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="U25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V25" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.18</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AB25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC25" t="n">
         <v>2.63</v>
       </c>
-      <c r="AC25" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD25" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF25" t="n">
         <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK25" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="O26" t="n">
-        <v>4.05</v>
+        <v>3.83</v>
       </c>
       <c r="P26" t="n">
-        <v>5.12</v>
+        <v>3.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="R26" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T26" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
         <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>1.37</v>
       </c>
       <c r="O27" t="n">
-        <v>3.83</v>
+        <v>5.06</v>
       </c>
       <c r="P27" t="n">
-        <v>3.91</v>
+        <v>8.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="R27" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="S27" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.04</v>
+        <v>2.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.86</v>
+        <v>3.3</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6323,10 +6323,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="O48" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="P48" t="n">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="O49" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="P49" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="P4" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T4" t="n">
         <v>2.57</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="O5" t="n">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="P5" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.91</v>
+        <v>2.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.87</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O14" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P14" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AE14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>7.27</v>
+        <v>3.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.85</v>
+        <v>3.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.44</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.26</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.1</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>2.48</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK16" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>3.01</v>
+        <v>3.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
-        <v>3.13</v>
+        <v>2.81</v>
       </c>
       <c r="P21" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="Q21" t="n">
         <v>2.9</v>
@@ -3761,49 +3761,49 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
         <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.83</v>
+        <v>2.49</v>
       </c>
       <c r="R23" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="S23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T23" t="n">
-        <v>3.55</v>
+        <v>2.77</v>
       </c>
       <c r="U23" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="V23" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P24" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.49</v>
+        <v>4.83</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.77</v>
+        <v>3.55</v>
       </c>
       <c r="U24" t="n">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4859,19 +4859,19 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -4880,10 +4880,10 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -4892,31 +4892,31 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5504,55 +5504,55 @@
         <v>1.78</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="O33" t="n">
-        <v>6.35</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>8.050000000000001</v>
+        <v>5.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,80 +5813,80 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>1.19</v>
       </c>
       <c r="O34" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="P34" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK34" t="n">
         <v>3.78</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,80 +5972,80 @@
         </is>
       </c>
       <c r="N35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK35" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O35" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P35" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6286,68 +6286,68 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6458,55 +6458,55 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.35</v>
+        <v>1.58</v>
       </c>
       <c r="O42" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>3.27</v>
+        <v>5.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>6.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="O46" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="P46" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7889,55 +7889,55 @@
         <v>2.59</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8048,28 +8048,28 @@
         <v>4.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y48" t="n">
         <v>1.51</v>
@@ -8078,25 +8078,25 @@
         <v>2.35</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>2.3</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O51" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="O53" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="P53" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9161,55 +9161,55 @@
         <v>8.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9479,34 +9479,34 @@
         <v>3.79</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA57" t="n">
         <v>1.77</v>
@@ -9515,19 +9515,19 @@
         <v>1.94</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9797,34 +9797,34 @@
         <v>5.31</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA59" t="n">
         <v>1.8</v>
@@ -9833,19 +9833,19 @@
         <v>1.86</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -9947,64 +9947,64 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,31 +1043,31 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.03</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
-        <v>3.74</v>
+        <v>2.41</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.51</v>
+        <v>3.42</v>
       </c>
       <c r="R4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T4" t="n">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -1076,31 +1076,31 @@
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,65 +1202,65 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF5" t="n">
         <v>2</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AG5" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.87</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.41</v>
+        <v>3.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.42</v>
+        <v>2.51</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="U6" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
@@ -1394,31 +1394,31 @@
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.22</v>
+        <v>3.07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.55</v>
+        <v>3.76</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="O7" t="n">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>4.95</v>
+        <v>3.54</v>
       </c>
       <c r="P14" t="n">
-        <v>7.27</v>
+        <v>3.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.85</v>
+        <v>3.24</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.44</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.26</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2.1</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>2.48</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>4.38</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>4.28</v>
       </c>
       <c r="P16" t="n">
-        <v>3.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.41</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U16" t="n">
         <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
         <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.38</v>
+        <v>1.37</v>
       </c>
       <c r="O17" t="n">
-        <v>4.28</v>
+        <v>4.95</v>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>7.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.3</v>
+        <v>4.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.37</v>
+        <v>2.09</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.38</v>
+        <v>2.75</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R20" t="n">
         <v>2</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.66</v>
+        <v>1.92</v>
       </c>
       <c r="O21" t="n">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="P21" t="n">
-        <v>3.01</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="P22" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>4.05</v>
+        <v>3.83</v>
       </c>
       <c r="P25" t="n">
-        <v>5.12</v>
+        <v>3.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="R25" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
         <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.89</v>
+        <v>1.37</v>
       </c>
       <c r="O26" t="n">
-        <v>3.83</v>
+        <v>5.06</v>
       </c>
       <c r="P26" t="n">
-        <v>3.91</v>
+        <v>8.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="R26" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="S26" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="V26" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.04</v>
+        <v>2.63</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.86</v>
+        <v>3.3</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="O27" t="n">
-        <v>5.06</v>
+        <v>4.05</v>
       </c>
       <c r="P27" t="n">
-        <v>8.25</v>
+        <v>5.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="R27" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="S27" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="U27" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y27" t="n">
         <v>1.18</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z27" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AB27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.63</v>
       </c>
-      <c r="AC27" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF27" t="n">
         <v>1.65</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="O33" t="n">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="P33" t="n">
-        <v>5.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="R33" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="S33" t="n">
         <v>1.09</v>
       </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V33" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="W33" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z33" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.71</v>
+        <v>3.78</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,80 +5813,80 @@
         </is>
       </c>
       <c r="N34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S34" t="n">
         <v>1.19</v>
       </c>
-      <c r="O34" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="P34" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="T34" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
         <v>1.53</v>
       </c>
-      <c r="R34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V34" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF34" t="n">
+      <c r="AK34" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>3.78</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>1.76</v>
       </c>
       <c r="R35" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="S35" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="T35" t="n">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="V35" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.44</v>
+        <v>2.71</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6127,68 +6127,68 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="O39" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="P39" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6763,68 +6763,68 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P42" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AB42" t="n">
         <v>1.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.51</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P43" t="n">
-        <v>6.78</v>
+        <v>2.85</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="O44" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="P44" t="n">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.8</v>
+        <v>1.51</v>
       </c>
       <c r="O46" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P46" t="n">
-        <v>2.23</v>
+        <v>6.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="O48" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="P48" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC48" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="O49" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="P49" t="n">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="O5" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>2.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="R5" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.54</v>
+        <v>3.22</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>3.54</v>
       </c>
       <c r="P6" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>3.54</v>
+        <v>3.26</v>
       </c>
       <c r="P7" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.54</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>4.38</v>
       </c>
       <c r="O14" t="n">
-        <v>3.54</v>
+        <v>4.28</v>
       </c>
       <c r="P14" t="n">
-        <v>3.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="U14" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.24</v>
+        <v>4.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.94</v>
+        <v>2.37</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.76</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>3.63</v>
+        <v>3.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.5</v>
+        <v>3.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.38</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>4.28</v>
+        <v>3.76</v>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>3.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>2.41</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
         <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W16" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF16" t="n">
         <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O19" t="n">
         <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>3.01</v>
+        <v>3.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="O22" t="n">
-        <v>3.13</v>
+        <v>2.81</v>
       </c>
       <c r="P22" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="Q22" t="n">
         <v>2.9</v>
@@ -3920,49 +3920,49 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.05</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P23" t="n">
-        <v>3.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.49</v>
+        <v>4.83</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="S23" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.77</v>
+        <v>3.55</v>
       </c>
       <c r="U23" t="n">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="V23" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>2.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>3.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.83</v>
+        <v>2.49</v>
       </c>
       <c r="R24" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T24" t="n">
-        <v>3.55</v>
+        <v>2.77</v>
       </c>
       <c r="U24" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="V24" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="O25" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>3.91</v>
+        <v>5.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V25" t="n">
         <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>4.05</v>
+        <v>3.83</v>
       </c>
       <c r="P27" t="n">
-        <v>5.12</v>
+        <v>3.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T27" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V27" t="n">
         <v>1.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="O30" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="P30" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="O31" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="O33" t="n">
-        <v>6.35</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>8.050000000000001</v>
+        <v>5.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="R33" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="S33" t="n">
         <v>1.09</v>
       </c>
       <c r="T33" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="V33" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z33" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK33" t="n">
-        <v>3.78</v>
+        <v>2.71</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,80 +5813,80 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>1.19</v>
       </c>
       <c r="O34" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="P34" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK34" t="n">
         <v>3.78</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,80 +5972,80 @@
         </is>
       </c>
       <c r="N35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK35" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O35" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="P35" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T35" t="n">
-        <v>5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V35" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>2.71</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P36" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AB36" t="n">
         <v>1.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>1.51</v>
       </c>
       <c r="O38" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P38" t="n">
-        <v>2.23</v>
+        <v>6.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6763,17 +6763,17 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6935,55 +6935,55 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="O42" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P42" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>3.16</v>
       </c>
       <c r="O43" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="P43" t="n">
-        <v>2.85</v>
+        <v>2.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.16</v>
+        <v>1.58</v>
       </c>
       <c r="O45" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.42</v>
+        <v>5.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.94</v>
+        <v>2.2</v>
       </c>
       <c r="R45" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S45" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="T45" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="U45" t="n">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="V45" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AC45" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.36</v>
+        <v>2.08</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,65 +7721,65 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
+        <v>4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z46" t="n">
         <v>2.1</v>
       </c>
-      <c r="R46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
-      <c r="X46" t="n">
+      <c r="AA46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE46" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y46" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AA46" t="n">
+      <c r="AF46" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AG46" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC46" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z50" t="n">
         <v>3.2</v>
       </c>
-      <c r="R50" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U50" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA50" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
-        <v>6.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA51" t="n">
         <v>3.4</v>
       </c>
-      <c r="R51" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.28</v>
+        <v>6.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="O53" t="n">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="P53" t="n">
-        <v>2.69</v>
+        <v>3.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="O54" t="n">
-        <v>2.86</v>
+        <v>3.72</v>
       </c>
       <c r="P54" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.05</v>
+        <v>2.87</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,52 +9152,52 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="O55" t="n">
-        <v>3.72</v>
+        <v>2.73</v>
       </c>
       <c r="P55" t="n">
-        <v>8.6</v>
+        <v>2.69</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="R55" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S55" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T55" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U55" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V55" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W55" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X55" t="n">
         <v>1.13</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC55" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AD55" t="n">
         <v>1.13</v>
@@ -9206,26 +9206,26 @@
         <v>1.03</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AG55" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK55" t="n">
-        <v>2.16</v>
+        <v>1.52</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N61" t="n">

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="O6" t="n">
-        <v>3.54</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,61 +1520,61 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.03</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T7" t="n">
-        <v>2.57</v>
+        <v>2.34</v>
       </c>
       <c r="U7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.07</v>
+        <v>2.54</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
         <v>1.8</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,55 +2006,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>4.95</v>
       </c>
       <c r="P16" t="n">
-        <v>3.63</v>
+        <v>7.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK16" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>4.95</v>
+        <v>3.76</v>
       </c>
       <c r="P17" t="n">
-        <v>7.27</v>
+        <v>3.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>2.41</v>
       </c>
       <c r="R17" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
-        <v>3.13</v>
+        <v>2.81</v>
       </c>
       <c r="P21" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="Q21" t="n">
         <v>2.9</v>
@@ -3761,49 +3761,49 @@
         <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
         <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.81</v>
+        <v>3.13</v>
       </c>
       <c r="P22" t="n">
-        <v>3.01</v>
+        <v>3.14</v>
       </c>
       <c r="Q22" t="n">
         <v>2.9</v>
@@ -3920,49 +3920,49 @@
         <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="O30" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="O31" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="P31" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="O33" t="n">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="P33" t="n">
-        <v>5.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="R33" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="S33" t="n">
         <v>1.09</v>
       </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V33" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="W33" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z33" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.71</v>
+        <v>3.78</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,80 +5813,80 @@
         </is>
       </c>
       <c r="N34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S34" t="n">
         <v>1.19</v>
       </c>
-      <c r="O34" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="P34" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="T34" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
         <v>1.53</v>
       </c>
-      <c r="R34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V34" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF34" t="n">
+      <c r="AK34" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>3.78</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>1.76</v>
       </c>
       <c r="R35" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="S35" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="T35" t="n">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="V35" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.44</v>
+        <v>2.71</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O36" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="P36" t="n">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="AB36" t="n">
         <v>1.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.51</v>
+        <v>2.28</v>
       </c>
       <c r="O38" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>6.78</v>
+        <v>2.85</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6617,55 +6617,55 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,52 +7403,52 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.35</v>
+        <v>1.58</v>
       </c>
       <c r="O44" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>3.27</v>
+        <v>5.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="R44" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S44" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="T44" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="U44" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="V44" t="n">
         <v>1.2</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
         <v>1.13</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AB44" t="n">
         <v>1.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AD44" t="n">
         <v>1.13</v>
@@ -7457,10 +7457,10 @@
         <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.18</v>
+        <v>2.57</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,65 +7562,65 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="O45" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P45" t="n">
-        <v>5.5</v>
+        <v>6.78</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R45" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S45" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="T45" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="U45" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="V45" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="O48" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="P48" t="n">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="O49" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="P49" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC49" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="O53" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="P53" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="O55" t="n">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="P55" t="n">
-        <v>2.69</v>
+        <v>3.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AC55" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -728,31 +728,31 @@
         <v>2.03</v>
       </c>
       <c r="O2" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="R2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
         <v>2.39</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -761,28 +761,28 @@
         <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF2" t="n">
         <v>1.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>1.42</v>
       </c>
       <c r="O3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P3" t="n">
-        <v>5.3</v>
+        <v>6.07</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P4" t="n">
         <v>2.57</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.87</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="P5" t="n">
-        <v>2.41</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.42</v>
+        <v>2.65</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="U5" t="n">
-        <v>3.04</v>
+        <v>3.19</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AF5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="P7" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
@@ -1535,13 +1535,13 @@
         <v>2.03</v>
       </c>
       <c r="S7" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="T7" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="U7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V7" t="n">
         <v>1.3</v>
@@ -1565,7 +1565,7 @@
         <v>1.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AD7" t="n">
         <v>1.15</v>
@@ -1577,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.73</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="R10" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
         <v>1.38</v>
@@ -2027,22 +2027,22 @@
         <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.25</v>
+        <v>3.63</v>
       </c>
       <c r="AD10" t="n">
         <v>1.3</v>
@@ -2054,7 +2054,7 @@
         <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2492,13 +2492,13 @@
         <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="U13" t="n">
         <v>2.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
         <v>1.11</v>
@@ -2507,28 +2507,28 @@
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z13" t="n">
         <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC13" t="n">
         <v>2.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG13" t="n">
         <v>2.38</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,34 +2633,34 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4.38</v>
+        <v>2.53</v>
       </c>
       <c r="O14" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
@@ -2672,25 +2672,25 @@
         <v>4.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
         <v>2.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
         <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="Q15" t="n">
         <v>2.6</v>
@@ -2807,13 +2807,13 @@
         <v>2.15</v>
       </c>
       <c r="S15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U15" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="V15" t="n">
         <v>1.36</v>
@@ -2831,25 +2831,25 @@
         <v>3.24</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
         <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>7.27</v>
+        <v>3.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>2.41</v>
       </c>
       <c r="R16" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.85</v>
+        <v>4.33</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="O17" t="n">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.63</v>
+        <v>5.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.29</v>
+        <v>2.58</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W17" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.64</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.83</v>
+        <v>2.84</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>6.76</v>
+        <v>5.5</v>
       </c>
       <c r="O18" t="n">
-        <v>5.16</v>
+        <v>4.65</v>
       </c>
       <c r="P18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.93</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="S18" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T18" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V18" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z18" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB18" t="n">
         <v>2.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE18" t="n">
         <v>1.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U19" t="n">
         <v>3.05</v>
       </c>
-      <c r="P19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O20" t="n">
         <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3746,19 +3746,19 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.66</v>
+        <v>2.21</v>
       </c>
       <c r="O21" t="n">
-        <v>2.81</v>
+        <v>3.12</v>
       </c>
       <c r="P21" t="n">
-        <v>3.01</v>
+        <v>3.42</v>
       </c>
       <c r="Q21" t="n">
         <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="S21" t="n">
         <v>1.47</v>
@@ -3800,10 +3800,10 @@
         <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="P22" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4064,55 +4064,55 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
-        <v>4.05</v>
+        <v>3.93</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.83</v>
+        <v>4.33</v>
       </c>
       <c r="R23" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="S23" t="n">
         <v>1.25</v>
       </c>
       <c r="T23" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="U23" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="n">
         <v>4.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AE23" t="n">
         <v>1.22</v>
@@ -4121,7 +4121,7 @@
         <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4223,31 +4223,31 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
         <v>2.1</v>
       </c>
       <c r="S24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T24" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="U24" t="n">
         <v>2.64</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W24" t="n">
         <v>1.04</v>
@@ -4259,7 +4259,7 @@
         <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AA24" t="n">
         <v>1.91</v>
@@ -4271,7 +4271,7 @@
         <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
         <v>1.07</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.65</v>
       </c>
-      <c r="O25" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P25" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AF25" t="n">
         <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,80 +4541,80 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.37</v>
+        <v>1.92</v>
       </c>
       <c r="O26" t="n">
-        <v>5.06</v>
+        <v>3.5</v>
       </c>
       <c r="P26" t="n">
-        <v>8.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.75</v>
+        <v>2.48</v>
       </c>
       <c r="R26" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="S26" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB26" t="n">
         <v>2.05</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>2.63</v>
       </c>
-      <c r="AC26" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK26" t="n">
-        <v>3.3</v>
+        <v>1.87</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="O27" t="n">
-        <v>3.83</v>
+        <v>4.04</v>
       </c>
       <c r="P27" t="n">
-        <v>3.91</v>
+        <v>4.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="R27" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S27" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U27" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V27" t="n">
         <v>1.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG27" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,80 +5654,80 @@
         </is>
       </c>
       <c r="N33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S33" t="n">
         <v>1.19</v>
       </c>
-      <c r="O33" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="P33" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="T33" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.53</v>
       </c>
-      <c r="R33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V33" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF33" t="n">
+      <c r="AK33" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>3.78</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,80 +5813,80 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.56</v>
+        <v>1.19</v>
       </c>
       <c r="O34" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="P34" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK34" t="n">
         <v>3.78</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.35</v>
+        <v>1.51</v>
       </c>
       <c r="O36" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="P36" t="n">
-        <v>3.27</v>
+        <v>6.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S36" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T36" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="U36" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC36" t="n">
-        <v>5.75</v>
+        <v>4.45</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.28</v>
+        <v>1.58</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P38" t="n">
-        <v>2.85</v>
+        <v>5.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S39" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="T39" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="U39" t="n">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="V39" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE39" t="n">
         <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AG39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK39" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="O40" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P40" t="n">
-        <v>3.7</v>
+        <v>2.23</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="S43" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="T43" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="U43" t="n">
-        <v>3.16</v>
+        <v>4.3</v>
       </c>
       <c r="V43" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="W43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK43" t="n">
         <v>1.36</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AB44" t="n">
         <v>1.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="O46" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P46" t="n">
-        <v>2.23</v>
+        <v>3.7</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U50" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA50" t="n">
         <v>3.4</v>
       </c>
-      <c r="R50" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U50" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.28</v>
+        <v>6.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O51" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z51" t="n">
         <v>3.2</v>
       </c>
-      <c r="R51" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U51" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA51" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="O53" t="n">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="P53" t="n">
-        <v>2.69</v>
+        <v>3.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,52 +8993,52 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.4</v>
+        <v>2.69</v>
       </c>
       <c r="O54" t="n">
-        <v>3.72</v>
+        <v>2.73</v>
       </c>
       <c r="P54" t="n">
-        <v>8.6</v>
+        <v>2.69</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="R54" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S54" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T54" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U54" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V54" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W54" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X54" t="n">
         <v>1.13</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC54" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AD54" t="n">
         <v>1.13</v>
@@ -9047,26 +9047,26 @@
         <v>1.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AG54" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK54" t="n">
-        <v>2.16</v>
+        <v>1.52</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="O55" t="n">
-        <v>2.86</v>
+        <v>3.72</v>
       </c>
       <c r="P55" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.05</v>
+        <v>2.87</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>2.73</v>
       </c>
       <c r="O5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.65</v>
+        <v>3.42</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T5" t="n">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="U5" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="AD5" t="n">
         <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.42</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T8" t="n">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="U8" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AD8" t="n">
         <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="R15" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.24</v>
+        <v>4.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.29</v>
+        <v>2.58</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="W16" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>2.84</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>5.75</v>
+        <v>3.45</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.8</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.21</v>
+        <v>3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.84</v>
+        <v>1.73</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U20" t="n">
         <v>3.05</v>
       </c>
-      <c r="P20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="O21" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="P21" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="O22" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="P22" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>1.91</v>
       </c>
       <c r="O23" t="n">
-        <v>3.93</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>1.63</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S23" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T23" t="n">
-        <v>3.42</v>
+        <v>2.68</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="V23" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>3.52</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.91</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>3.93</v>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R24" t="n">
         <v>2.5</v>
       </c>
-      <c r="R24" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.52</v>
+        <v>4.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="O25" t="n">
-        <v>4.6</v>
+        <v>4.04</v>
       </c>
       <c r="P25" t="n">
-        <v>6.7</v>
+        <v>4.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.22</v>
       </c>
-      <c r="T25" t="n">
-        <v>4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.15</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AK25" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,65 +4700,65 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="O27" t="n">
-        <v>4.04</v>
+        <v>4.6</v>
       </c>
       <c r="P27" t="n">
-        <v>4.95</v>
+        <v>6.7</v>
       </c>
       <c r="Q27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.1</v>
       </c>
-      <c r="R27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG27" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>6.35</v>
+        <v>5.25</v>
       </c>
       <c r="P34" t="n">
-        <v>8.050000000000001</v>
+        <v>5.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="R34" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="S34" t="n">
         <v>1.09</v>
       </c>
       <c r="T34" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="V34" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="W34" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X34" t="n">
         <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK34" t="n">
-        <v>3.78</v>
+        <v>2.71</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="O35" t="n">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="P35" t="n">
-        <v>5.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="R35" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="S35" t="n">
         <v>1.09</v>
       </c>
       <c r="T35" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V35" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z35" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG35" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.71</v>
+        <v>3.78</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.51</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P36" t="n">
-        <v>6.78</v>
+        <v>2.23</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P38" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AB38" t="n">
         <v>1.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.35</v>
+        <v>1.51</v>
       </c>
       <c r="O39" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="P39" t="n">
-        <v>3.27</v>
+        <v>6.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S39" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T39" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="U39" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="V39" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC39" t="n">
-        <v>5.75</v>
+        <v>4.45</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.8</v>
+        <v>1.58</v>
       </c>
       <c r="O40" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P40" t="n">
-        <v>2.23</v>
+        <v>5.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="S42" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="T42" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="U42" t="n">
-        <v>3.16</v>
+        <v>4.3</v>
       </c>
       <c r="V42" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="W42" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK42" t="n">
         <v>1.36</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.42</v>
+        <v>2.65</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="U5" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
         <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="P6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.57</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>2.73</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.65</v>
+        <v>3.42</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T8" t="n">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="U8" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="AD8" t="n">
         <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,55 +2006,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.53</v>
+        <v>1.91</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S14" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA14" t="n">
         <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
         <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.29</v>
+        <v>2.58</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>2.84</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.41</v>
+        <v>2.53</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>5.75</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T16" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.09</v>
+        <v>2.39</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.84</v>
+        <v>1.48</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O19" t="n">
         <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="P20" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="P21" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>6.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.48</v>
+        <v>1.75</v>
       </c>
       <c r="R26" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S26" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
-        <v>2.54</v>
+        <v>2.13</v>
       </c>
       <c r="V26" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="O27" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>6.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.75</v>
+        <v>2.48</v>
       </c>
       <c r="R27" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S27" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
-        <v>2.13</v>
+        <v>2.54</v>
       </c>
       <c r="V27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.67</v>
       </c>
-      <c r="W27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AB27" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>5.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>1.76</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="S33" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="T33" t="n">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="U33" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="V33" t="n">
-        <v>1.68</v>
+        <v>2.11</v>
       </c>
       <c r="W33" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.44</v>
+        <v>2.71</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="O34" t="n">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="P34" t="n">
-        <v>5.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="R34" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="S34" t="n">
         <v>1.09</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V34" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="W34" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="X34" t="n">
         <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z34" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB34" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG34" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.71</v>
+        <v>3.78</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,80 +5972,80 @@
         </is>
       </c>
       <c r="N35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S35" t="n">
         <v>1.19</v>
       </c>
-      <c r="O35" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="P35" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="Q35" t="n">
+      <c r="T35" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35" t="n">
         <v>1.53</v>
       </c>
-      <c r="R35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V35" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF35" t="n">
+      <c r="AK35" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>3.78</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,65 +6608,65 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
+        <v>4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z39" t="n">
         <v>2.1</v>
       </c>
-      <c r="R39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
-      <c r="X39" t="n">
+      <c r="AA39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="AF39" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AG39" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC39" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,28 +6767,28 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.58</v>
+        <v>2.19</v>
       </c>
       <c r="O40" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="P40" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.2</v>
+        <v>3.06</v>
       </c>
       <c r="R40" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S40" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="T40" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="U40" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="V40" t="n">
         <v>1.2</v>
@@ -6797,7 +6797,7 @@
         <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y40" t="n">
         <v>1.57</v>
@@ -6812,7 +6812,7 @@
         <v>1.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AD40" t="n">
         <v>1.13</v>
@@ -6821,10 +6821,10 @@
         <v>1.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.57</v>
+        <v>2.15</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S42" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="T42" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="U42" t="n">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
       <c r="V42" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE42" t="n">
         <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.36</v>
+        <v>2.08</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="O43" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P43" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,80 +7562,80 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.35</v>
+        <v>3.16</v>
       </c>
       <c r="O45" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="P45" t="n">
-        <v>3.27</v>
+        <v>2.42</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>3.98</v>
       </c>
       <c r="R45" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="S45" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45" t="n">
         <v>1.5</v>
       </c>
-      <c r="T45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U45" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AK45" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="O46" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="P46" t="n">
-        <v>3.7</v>
+        <v>6.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="O53" t="n">
-        <v>2.86</v>
+        <v>3.72</v>
       </c>
       <c r="P53" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>2.87</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="O55" t="n">
-        <v>3.72</v>
+        <v>2.86</v>
       </c>
       <c r="P55" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AC55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="O5" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="O6" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z6" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.54</v>
-      </c>
       <c r="AA6" t="n">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="P7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.42</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T8" t="n">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="U8" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AD8" t="n">
         <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.29</v>
+        <v>2.58</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>2.84</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>5.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>2.41</v>
       </c>
       <c r="R15" t="n">
-        <v>2.58</v>
+        <v>2.29</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.21</v>
+        <v>2.48</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.84</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3761,19 +3761,19 @@
         <v>1.83</v>
       </c>
       <c r="S21" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="T21" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
         <v>1.06</v>
@@ -3797,7 +3797,7 @@
         <v>1.21</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF21" t="n">
         <v>1.86</v>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.91</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>3.93</v>
       </c>
       <c r="P23" t="n">
-        <v>3.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R23" t="n">
         <v>2.5</v>
       </c>
-      <c r="R23" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S23" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="U23" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.52</v>
+        <v>4.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>1.91</v>
       </c>
       <c r="O24" t="n">
-        <v>3.93</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
-        <v>1.63</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>2.68</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="V24" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.8</v>
+        <v>3.52</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,49 +4382,49 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
-        <v>4.04</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>4.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="R25" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
         <v>2.63</v>
@@ -4433,13 +4433,13 @@
         <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,49 +4700,49 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>4.04</v>
       </c>
       <c r="P27" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T27" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q27" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U27" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="V27" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC27" t="n">
         <v>2.63</v>
@@ -4751,13 +4751,13 @@
         <v>1.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="O30" t="n">
-        <v>2.9</v>
+        <v>4.65</v>
       </c>
       <c r="P30" t="n">
-        <v>4.4</v>
+        <v>8.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="O31" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="O37" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="P37" t="n">
         <v>2.85</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S39" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="T39" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="U39" t="n">
-        <v>4.3</v>
+        <v>3.72</v>
       </c>
       <c r="V39" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE39" t="n">
         <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.36</v>
+        <v>2.08</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.19</v>
+        <v>3.16</v>
       </c>
       <c r="O40" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="P40" t="n">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.06</v>
+        <v>3.96</v>
       </c>
       <c r="R40" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="S40" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="T40" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="U40" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="W40" t="n">
         <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AC40" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,80 +7085,80 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S42" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="T42" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="U42" t="n">
-        <v>3.72</v>
+        <v>4.3</v>
       </c>
       <c r="V42" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE42" t="n">
         <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="AG42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.44</v>
       </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK42" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" t="n">
         <v>2.8</v>
       </c>
-      <c r="O44" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P44" t="n">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.16</v>
+        <v>1.51</v>
       </c>
       <c r="O45" t="n">
-        <v>2.91</v>
+        <v>3.45</v>
       </c>
       <c r="P45" t="n">
-        <v>2.42</v>
+        <v>6.78</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.98</v>
+        <v>2.1</v>
       </c>
       <c r="R45" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S45" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y45" t="n">
         <v>1.47</v>
       </c>
-      <c r="T45" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U45" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z45" t="n">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.51</v>
+        <v>2.28</v>
       </c>
       <c r="O46" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P46" t="n">
-        <v>6.78</v>
+        <v>2.85</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7880,19 +7880,19 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="O47" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="P47" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S47" t="n">
         <v>1.44</v>
@@ -7901,16 +7901,16 @@
         <v>2.5</v>
       </c>
       <c r="U47" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="V47" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W47" t="n">
         <v>1.06</v>
       </c>
       <c r="X47" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
         <v>1.37</v>
@@ -7919,25 +7919,25 @@
         <v>3.19</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF47" t="n">
         <v>1.83</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="O48" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="P48" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC48" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="O49" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="P49" t="n">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z50" t="n">
         <v>3.2</v>
       </c>
-      <c r="R50" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U50" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA50" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
-        <v>6.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA51" t="n">
         <v>3.4</v>
       </c>
-      <c r="R51" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB51" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.28</v>
+        <v>6.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="O53" t="n">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="P53" t="n">
-        <v>8.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,52 +8993,52 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="O54" t="n">
-        <v>2.73</v>
+        <v>3.72</v>
       </c>
       <c r="P54" t="n">
-        <v>2.69</v>
+        <v>8.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="R54" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S54" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T54" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U54" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V54" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X54" t="n">
         <v>1.13</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC54" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AD54" t="n">
         <v>1.13</v>
@@ -9047,10 +9047,10 @@
         <v>1.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.52</v>
+        <v>2.16</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="O55" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="P55" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9479,55 +9479,55 @@
         <v>3.79</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R57" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S57" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T57" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="U57" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V57" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W57" t="n">
         <v>1.06</v>
       </c>
       <c r="X57" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD57" t="n">
         <v>1.3</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF57" t="n">
         <v>1.75</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="R2" t="n">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="S2" t="n">
         <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U2" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V2" t="n">
         <v>1.5</v>
@@ -758,10 +758,10 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
         <v>1.64</v>
@@ -779,10 +779,10 @@
         <v>1.12</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P3" t="n">
-        <v>6.07</v>
+        <v>6.24</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2.4</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="S7" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="T7" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.54</v>
+        <v>2.86</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>2.61</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="P8" t="n">
-        <v>3.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T8" t="n">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="U8" t="n">
-        <v>3.19</v>
+        <v>3.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
         <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2486,10 +2486,10 @@
         <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T13" t="n">
         <v>3.44</v>
@@ -2507,31 +2507,31 @@
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
         <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.29</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P14" t="n">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.84</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.5</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.53</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>6.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="S16" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T16" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.54</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.48</v>
+        <v>2.71</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="P17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.45</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.73</v>
-      </c>
       <c r="U17" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.24</v>
+        <v>4.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3272,25 +3272,25 @@
         <v>5.5</v>
       </c>
       <c r="O18" t="n">
-        <v>4.65</v>
+        <v>4.68</v>
       </c>
       <c r="P18" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
         <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
         <v>1.67</v>
@@ -3299,7 +3299,7 @@
         <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.09</v>
@@ -3314,10 +3314,10 @@
         <v>2.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="n">
         <v>1.25</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="P19" t="n">
-        <v>3.8</v>
+        <v>4.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF20" t="n">
         <v>2</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3755,31 +3755,31 @@
         <v>3.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="R21" t="n">
         <v>1.83</v>
       </c>
       <c r="S21" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T21" t="n">
         <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
         <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
         <v>2.9</v>
@@ -3800,7 +3800,7 @@
         <v>1.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
         <v>1.83</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
         <v>1.53</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="O22" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="P22" t="n">
-        <v>3.42</v>
+        <v>2.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>1.9</v>
       </c>
       <c r="O23" t="n">
-        <v>3.93</v>
+        <v>3.48</v>
       </c>
       <c r="P23" t="n">
-        <v>1.63</v>
+        <v>3.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S23" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T23" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2</v>
+        <v>2.84</v>
       </c>
       <c r="V23" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="W23" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.33</v>
+        <v>3.12</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.91</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
-        <v>3.2</v>
+        <v>3.93</v>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>3.98</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="S24" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T24" t="n">
-        <v>2.68</v>
+        <v>3.75</v>
       </c>
       <c r="U24" t="n">
-        <v>2.64</v>
+        <v>2.22</v>
       </c>
       <c r="V24" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.52</v>
+        <v>4.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>4.04</v>
       </c>
       <c r="P25" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T25" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q25" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U25" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="V25" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG25" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>1.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="O26" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="P26" t="n">
-        <v>6.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="R26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S26" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z26" t="n">
         <v>4</v>
       </c>
-      <c r="U26" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V26" t="n">
+      <c r="AA26" t="n">
         <v>1.67</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AB26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.15</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AF26" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AK26" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,65 +4700,65 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="O27" t="n">
-        <v>4.04</v>
+        <v>4.95</v>
       </c>
       <c r="P27" t="n">
-        <v>4.95</v>
+        <v>6.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="R27" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S27" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T27" t="n">
-        <v>3.15</v>
+        <v>3.66</v>
       </c>
       <c r="U27" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.35</v>
+        <v>5.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="AB27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG27" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,80 +5177,80 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="O30" t="n">
-        <v>4.65</v>
+        <v>2.95</v>
       </c>
       <c r="P30" t="n">
-        <v>8.15</v>
+        <v>4.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK30" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="O31" t="n">
-        <v>2.9</v>
+        <v>4.95</v>
       </c>
       <c r="P31" t="n">
-        <v>4.4</v>
+        <v>9.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5504,22 +5504,22 @@
         <v>1.78</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.52</v>
+        <v>4.1</v>
       </c>
       <c r="R32" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="S32" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T32" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U32" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W32" t="n">
         <v>1.14</v>
@@ -5528,47 +5528,47 @@
         <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="AA32" t="n">
         <v>1.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.22</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="O33" t="n">
-        <v>5.25</v>
+        <v>6.55</v>
       </c>
       <c r="P33" t="n">
-        <v>5.32</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="R33" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="S33" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V33" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z33" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.71</v>
+        <v>3.7</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="O34" t="n">
-        <v>6.35</v>
+        <v>5.2</v>
       </c>
       <c r="P34" t="n">
-        <v>8.050000000000001</v>
+        <v>6.11</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="R34" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T34" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U34" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="V34" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="W34" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X34" t="n">
         <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK34" t="n">
-        <v>3.78</v>
+        <v>2.64</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5972,61 +5972,61 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="O35" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="R35" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S35" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T35" t="n">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="U35" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="W35" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X35" t="n">
         <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AG35" t="n">
         <v>2.7</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.58</v>
+        <v>3.16</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="P39" t="n">
-        <v>5.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.2</v>
+        <v>3.71</v>
       </c>
       <c r="R39" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="S39" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="T39" t="n">
-        <v>2.18</v>
+        <v>2.59</v>
       </c>
       <c r="U39" t="n">
-        <v>3.72</v>
+        <v>3.22</v>
       </c>
       <c r="V39" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W39" t="n">
         <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="AB39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC39" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK39" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.16</v>
+        <v>1.48</v>
       </c>
       <c r="O40" t="n">
-        <v>2.91</v>
+        <v>3.65</v>
       </c>
       <c r="P40" t="n">
-        <v>2.42</v>
+        <v>6</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.96</v>
+        <v>2.23</v>
       </c>
       <c r="R40" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S40" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="T40" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U40" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="V40" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="R42" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="S42" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="T42" t="n">
-        <v>2.02</v>
+        <v>2.67</v>
       </c>
       <c r="U42" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="V42" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X42" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AE42" t="n">
         <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="O43" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="P43" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="O44" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="P44" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6.78</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.1</v>
+        <v>2.91</v>
       </c>
       <c r="R45" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S45" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T45" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U45" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="V45" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB45" t="n">
         <v>1.53</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.45</v>
+        <v>4.05</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE45" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="O46" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P46" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7889,10 +7889,10 @@
         <v>2.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S47" t="n">
         <v>1.44</v>
@@ -7916,7 +7916,7 @@
         <v>1.37</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="AA47" t="n">
         <v>2.1</v>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>1.8</v>
       </c>
       <c r="O49" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="Q49" t="n">
         <v>2.45</v>
@@ -8213,49 +8213,49 @@
         <v>1.95</v>
       </c>
       <c r="S49" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T49" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="U49" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="V49" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X49" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.87</v>
+        <v>2.59</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC49" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD49" t="n">
         <v>1.13</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>2.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="R50" t="n">
         <v>2.15</v>
@@ -8378,7 +8378,7 @@
         <v>2.83</v>
       </c>
       <c r="U50" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V50" t="n">
         <v>1.36</v>
@@ -8387,34 +8387,34 @@
         <v>1.06</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z50" t="n">
         <v>3.2</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AD50" t="n">
         <v>1.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>1.25</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="O51" t="n">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="P51" t="n">
-        <v>3.83</v>
+        <v>3.26</v>
       </c>
       <c r="Q51" t="n">
         <v>3.2</v>
@@ -8531,13 +8531,13 @@
         <v>1.83</v>
       </c>
       <c r="S51" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="T51" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="U51" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V51" t="n">
         <v>1.15</v>
@@ -8549,16 +8549,16 @@
         <v>1.15</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC51" t="n">
         <v>6.5</v>
@@ -8567,13 +8567,13 @@
         <v>1.1</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>1.44</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8675,65 +8675,65 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="O52" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P52" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="R52" t="n">
         <v>2.63</v>
       </c>
       <c r="S52" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W52" t="n">
         <v>1.18</v>
       </c>
-      <c r="T52" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.19</v>
-      </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.15</v>
+        <v>6.07</v>
       </c>
       <c r="AA52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF52" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AG52" t="n">
         <v>2.9</v>
       </c>
-      <c r="AC52" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>3</v>
-      </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O53" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="P53" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA53" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF53" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB53" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="O54" t="n">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="P54" t="n">
-        <v>8.6</v>
+        <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AC54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,52 +9152,52 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.69</v>
+        <v>1.56</v>
       </c>
       <c r="O55" t="n">
-        <v>2.73</v>
+        <v>3.32</v>
       </c>
       <c r="P55" t="n">
-        <v>2.69</v>
+        <v>5.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="R55" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S55" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T55" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U55" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="V55" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X55" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC55" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AD55" t="n">
         <v>1.13</v>
@@ -9206,10 +9206,10 @@
         <v>1.03</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.52</v>
+        <v>2.18</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9479,7 +9479,7 @@
         <v>3.79</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R57" t="n">
         <v>2.2</v>
@@ -9488,7 +9488,7 @@
         <v>1.37</v>
       </c>
       <c r="T57" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="U57" t="n">
         <v>2.88</v>
@@ -9503,25 +9503,25 @@
         <v>1</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF57" t="n">
         <v>1.75</v>
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="O58" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="P58" t="n">
-        <v>3.9</v>
+        <v>4.74</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9800,7 +9800,7 @@
         <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S59" t="n">
         <v>1.32</v>
@@ -9809,7 +9809,7 @@
         <v>2.92</v>
       </c>
       <c r="U59" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="V59" t="n">
         <v>1.39</v>
@@ -9821,7 +9821,7 @@
         <v>1.04</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z59" t="n">
         <v>3.5</v>
@@ -9830,10 +9830,10 @@
         <v>1.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AD59" t="n">
         <v>1.3</v>
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK59" t="n">
         <v>2.3</v>
@@ -9947,37 +9947,37 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="O60" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P60" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="R60" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="S60" t="n">
         <v>1.53</v>
       </c>
       <c r="T60" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="U60" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="V60" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W60" t="n">
         <v>1.02</v>
       </c>
       <c r="X60" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y60" t="n">
         <v>1.44</v>
@@ -9992,13 +9992,13 @@
         <v>1.53</v>
       </c>
       <c r="AC60" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF60" t="n">
         <v>2.05</v>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="O4" t="n">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="P4" t="n">
-        <v>3.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="AA4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.44</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.57</v>
+        <v>3.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="P8" t="n">
-        <v>2.37</v>
+        <v>3.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T8" t="n">
-        <v>2.79</v>
+        <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.02</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.96</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>2.71</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="O15" t="n">
-        <v>3.29</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="Q15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.6</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="O16" t="n">
-        <v>4.9</v>
+        <v>3.29</v>
       </c>
       <c r="P16" t="n">
-        <v>6.6</v>
+        <v>3.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
-        <v>2.58</v>
+        <v>2.15</v>
       </c>
       <c r="S16" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="V16" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.21</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.71</v>
+        <v>1.73</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="P19" t="n">
-        <v>4.69</v>
+        <v>3.14</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.34</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.47</v>
-      </c>
       <c r="U19" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="V19" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
         <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O21" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="S21" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
         <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.31</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="P22" t="n">
-        <v>2.94</v>
+        <v>4.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,65 +4382,65 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="O25" t="n">
-        <v>4.04</v>
+        <v>4.95</v>
       </c>
       <c r="P25" t="n">
-        <v>4.95</v>
+        <v>6.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="R25" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T25" t="n">
-        <v>3.15</v>
+        <v>3.66</v>
       </c>
       <c r="U25" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG25" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC25" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="O27" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="P27" t="n">
         <v>4.95</v>
       </c>
-      <c r="P27" t="n">
-        <v>6.7</v>
-      </c>
       <c r="Q27" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="R27" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S27" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T27" t="n">
-        <v>3.66</v>
+        <v>3.15</v>
       </c>
       <c r="U27" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="V27" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.21</v>
+        <v>2.51</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AK27" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>2.88</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.82</v>
+        <v>1.31</v>
       </c>
       <c r="O30" t="n">
-        <v>2.95</v>
+        <v>4.95</v>
       </c>
       <c r="P30" t="n">
-        <v>4.75</v>
+        <v>9.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,80 +5336,80 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.31</v>
+        <v>1.82</v>
       </c>
       <c r="O31" t="n">
-        <v>4.95</v>
+        <v>2.95</v>
       </c>
       <c r="P31" t="n">
-        <v>9.1</v>
+        <v>4.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK31" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,80 +5654,80 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.19</v>
+        <v>2.42</v>
       </c>
       <c r="O33" t="n">
-        <v>6.55</v>
+        <v>3.9</v>
       </c>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>2.22</v>
       </c>
       <c r="Q33" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.53</v>
       </c>
-      <c r="R33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF33" t="n">
+      <c r="AK33" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>3.7</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.42</v>
+        <v>1.19</v>
       </c>
       <c r="O35" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="P35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB35" t="n">
         <v>3.9</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T35" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF35" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AG35" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.53</v>
+        <v>1.07</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.44</v>
+        <v>3.7</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>3.49</v>
       </c>
       <c r="R36" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="S36" t="n">
-        <v>1.69</v>
+        <v>1.38</v>
       </c>
       <c r="T36" t="n">
-        <v>2.04</v>
+        <v>2.73</v>
       </c>
       <c r="U36" t="n">
-        <v>4.25</v>
+        <v>2.56</v>
       </c>
       <c r="V36" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X36" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.4</v>
+        <v>1.78</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AC36" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>3.16</v>
+        <v>2.28</v>
       </c>
       <c r="O39" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.71</v>
+        <v>2.94</v>
       </c>
       <c r="R39" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="S39" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T39" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="U39" t="n">
-        <v>3.22</v>
+        <v>2.92</v>
       </c>
       <c r="V39" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
         <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.48</v>
+        <v>3.16</v>
       </c>
       <c r="O40" t="n">
-        <v>3.65</v>
+        <v>2.91</v>
       </c>
       <c r="P40" t="n">
-        <v>6</v>
+        <v>2.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.23</v>
+        <v>3.96</v>
       </c>
       <c r="R40" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="S40" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T40" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U40" t="n">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="V40" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.6</v>
+        <v>3.98</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE40" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.49</v>
+        <v>2.91</v>
       </c>
       <c r="R41" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="S41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y41" t="n">
         <v>1.38</v>
       </c>
-      <c r="T41" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U41" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.22</v>
-      </c>
       <c r="Z41" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.78</v>
+        <v>2.37</v>
       </c>
       <c r="AB41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF41" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG41" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>1.48</v>
       </c>
       <c r="O42" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="P42" t="n">
-        <v>2.85</v>
+        <v>6</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.94</v>
+        <v>2.23</v>
       </c>
       <c r="R42" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="S42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y42" t="n">
         <v>1.38</v>
       </c>
-      <c r="T42" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z42" t="n">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="AA42" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.76</v>
+        <v>2.32</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="S43" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="T43" t="n">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="U43" t="n">
-        <v>3.42</v>
+        <v>4.25</v>
       </c>
       <c r="V43" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="W43" t="n">
         <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="O46" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="P46" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>2.61</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>3.26</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R50" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="S50" t="n">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="T50" t="n">
-        <v>2.83</v>
+        <v>2.11</v>
       </c>
       <c r="U50" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="W50" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.85</v>
+        <v>3.19</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="O51" t="n">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>3.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z51" t="n">
         <v>3.2</v>
       </c>
-      <c r="R51" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U51" t="n">
-        <v>4</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA51" t="n">
-        <v>3.19</v>
+        <v>1.85</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P54" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z54" t="n">
         <v>2.25</v>
       </c>
-      <c r="O54" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P54" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
       <c r="AA54" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.56</v>
+        <v>2.15</v>
       </c>
       <c r="O55" t="n">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="P55" t="n">
-        <v>5.7</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AC55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9503,19 +9503,19 @@
         <v>1</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB57" t="n">
         <v>1.85</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD57" t="n">
         <v>1.27</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU61"/>
+  <dimension ref="A1:AU60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.61</v>
+        <v>2.04</v>
       </c>
       <c r="O4" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>3.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="O5" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U5" t="n">
         <v>3.04</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>4.9</v>
+        <v>3.53</v>
       </c>
       <c r="P14" t="n">
-        <v>6.6</v>
+        <v>2.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.14</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.71</v>
+        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,65 +3110,65 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.23</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.53</v>
+        <v>4.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.99</v>
+        <v>6.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="S17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.25</v>
       </c>
-      <c r="T17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AF17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.48</v>
+        <v>2.71</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O18" t="n">
-        <v>4.68</v>
+        <v>4.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
         <v>5</v>
@@ -3287,16 +3287,16 @@
         <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="V18" t="n">
         <v>1.67</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U21" t="n">
         <v>3.2</v>
       </c>
-      <c r="P21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3.1</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE21" t="n">
         <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.56</v>
+        <v>1.94</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>2.31</v>
       </c>
       <c r="O22" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="P22" t="n">
-        <v>4.69</v>
+        <v>2.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="O25" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="P25" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q25" t="n">
         <v>1.75</v>
@@ -4397,7 +4397,7 @@
         <v>2.63</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T25" t="n">
         <v>3.66</v>
@@ -4409,7 +4409,7 @@
         <v>1.66</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
         <v>1.02</v>
@@ -4418,7 +4418,7 @@
         <v>1.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="AA25" t="n">
         <v>1.47</v>
@@ -4436,7 +4436,7 @@
         <v>1.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
         <v>2.15</v>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="O26" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
         <v>2.3</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T26" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U26" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
         <v>4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="O27" t="n">
-        <v>4.04</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>4.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="R27" t="n">
         <v>2.3</v>
       </c>
       <c r="S27" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U27" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z27" t="n">
         <v>4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O30" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="P30" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.82</v>
+        <v>4.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.95</v>
+        <v>4.04</v>
       </c>
       <c r="P31" t="n">
-        <v>4.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.63</v>
+        <v>4.1</v>
       </c>
       <c r="R31" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="S31" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="T31" t="n">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="U31" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.3</v>
+        <v>4.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.5</v>
+        <v>2.08</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.13</v>
+        <v>1.66</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>46215.58333333334</v>
+        <v>46215.59375</v>
       </c>
     </row>
     <row r="32">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="O32" t="n">
-        <v>4.04</v>
+        <v>3.9</v>
       </c>
       <c r="P32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AE32" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46215.59375</v>
+        <v>46215.625</v>
       </c>
     </row>
     <row r="33">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.42</v>
+        <v>1.36</v>
       </c>
       <c r="O33" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.22</v>
+        <v>6.11</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.96</v>
+        <v>1.75</v>
       </c>
       <c r="R33" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA33" t="n">
         <v>1.18</v>
       </c>
-      <c r="T33" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AB33" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.44</v>
+        <v>2.64</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="O34" t="n">
-        <v>5.2</v>
+        <v>6.55</v>
       </c>
       <c r="P34" t="n">
-        <v>6.11</v>
+        <v>7</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="R34" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S34" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="T34" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="V34" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="W34" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
         <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z34" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AB34" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG34" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.64</v>
+        <v>3.7</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,65 +5972,65 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="O35" t="n">
-        <v>6.55</v>
+        <v>3.56</v>
       </c>
       <c r="P35" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Q35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.53</v>
       </c>
-      <c r="R35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.53</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK35" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6084,12 +6084,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.78</v>
+        <v>1.63</v>
       </c>
       <c r="O36" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="P36" t="n">
-        <v>2.27</v>
+        <v>5.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>46215.66666666666</v>
+        <v>46215.64583333334</v>
       </c>
     </row>
     <row r="37">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="O37" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
         <v>1.85</v>
@@ -6308,10 +6308,10 @@
         <v>1.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="U37" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="V37" t="n">
         <v>1.21</v>
@@ -6320,22 +6320,22 @@
         <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y37" t="n">
         <v>1.57</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AA37" t="n">
         <v>2.7</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AD37" t="n">
         <v>1.13</v>
@@ -6344,10 +6344,10 @@
         <v>1.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,52 +6449,52 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="O38" t="n">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="P38" t="n">
-        <v>5.25</v>
+        <v>2.85</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.29</v>
+        <v>3.06</v>
       </c>
       <c r="R38" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S38" t="n">
         <v>1.6</v>
       </c>
       <c r="T38" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="U38" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="V38" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W38" t="n">
         <v>1.01</v>
       </c>
       <c r="X38" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AC38" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AD38" t="n">
         <v>1.13</v>
@@ -6503,10 +6503,10 @@
         <v>1.03</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,80 +6767,80 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.16</v>
+        <v>2.23</v>
       </c>
       <c r="O40" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="P40" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.96</v>
+        <v>2.94</v>
       </c>
       <c r="R40" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="S40" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.59</v>
+        <v>2.31</v>
       </c>
       <c r="U40" t="n">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="V40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.29</v>
       </c>
-      <c r="W40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AK40" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.91</v>
+        <v>3.49</v>
       </c>
       <c r="R41" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="S41" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="T41" t="n">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="U41" t="n">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="V41" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.37</v>
+        <v>1.78</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
-        <v>4.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.23</v>
+        <v>2.91</v>
       </c>
       <c r="R42" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="S42" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T42" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="U42" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="V42" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
         <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE42" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="R43" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="S43" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="T43" t="n">
-        <v>2.04</v>
+        <v>2.59</v>
       </c>
       <c r="U43" t="n">
-        <v>4.25</v>
+        <v>3.22</v>
       </c>
       <c r="V43" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AC43" t="n">
-        <v>5</v>
+        <v>3.98</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>1.4</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="O45" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="P45" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.23</v>
+        <v>1.56</v>
       </c>
       <c r="O46" t="n">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="P46" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.94</v>
+        <v>2.15</v>
       </c>
       <c r="R46" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S46" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="T46" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="U46" t="n">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="V46" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE46" t="n">
         <v>1.03</v>
       </c>
-      <c r="X46" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF46" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.52</v>
+        <v>2.18</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,80 +7880,80 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="S47" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
         <v>1.44</v>
       </c>
-      <c r="T47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK47" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46215.67708333334</v>
+        <v>46215.66666666666</v>
       </c>
     </row>
     <row r="48">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.63</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P48" t="n">
-        <v>5.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>46215.6875</v>
+        <v>46215.67708333334</v>
       </c>
     </row>
     <row r="49">
@@ -8216,7 +8216,7 @@
         <v>1.57</v>
       </c>
       <c r="T49" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="U49" t="n">
         <v>3.76</v>
@@ -8231,10 +8231,10 @@
         <v>1.11</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AA49" t="n">
         <v>2.59</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>3.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z50" t="n">
         <v>3.2</v>
       </c>
-      <c r="R50" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U50" t="n">
-        <v>4</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA50" t="n">
-        <v>3.19</v>
+        <v>1.85</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="S51" t="n">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="T51" t="n">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="V51" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="W51" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.85</v>
+        <v>3.19</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O53" t="n">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="P53" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,40 +8993,40 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="O54" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P54" t="n">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="R54" t="n">
         <v>1.95</v>
       </c>
       <c r="S54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y54" t="n">
         <v>1.59</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U54" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.57</v>
       </c>
       <c r="Z54" t="n">
         <v>2.25</v>
@@ -9047,10 +9047,10 @@
         <v>1.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK54" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9105,12 +9105,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>46215.75</v>
+        <v>46215.76041666666</v>
       </c>
     </row>
     <row r="56">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="AU56" s="3" t="n">
-        <v>46215.76041666666</v>
+        <v>46215.79166666666</v>
       </c>
     </row>
     <row r="57">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,64 +9470,64 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="O57" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P57" t="n">
-        <v>3.79</v>
+        <v>4.74</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="R57" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S57" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T57" t="n">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="U57" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="V57" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="W57" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X57" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>46215.79166666666</v>
+        <v>46215.8125</v>
       </c>
     </row>
     <row r="58">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="O58" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="P58" t="n">
-        <v>4.74</v>
+        <v>5.31</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="R58" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="S58" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T58" t="n">
-        <v>2.53</v>
+        <v>2.92</v>
       </c>
       <c r="U58" t="n">
-        <v>3.04</v>
+        <v>2.63</v>
       </c>
       <c r="V58" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD58" t="n">
         <v>1.3</v>
       </c>
-      <c r="W58" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE58" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF58" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46215.8125</v>
+        <v>46215.83333333334</v>
       </c>
     </row>
     <row r="59">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.55</v>
+        <v>2.42</v>
       </c>
       <c r="O59" t="n">
-        <v>3.9</v>
+        <v>2.99</v>
       </c>
       <c r="P59" t="n">
-        <v>5.31</v>
+        <v>2.95</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>3.14</v>
       </c>
       <c r="R59" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="S59" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="T59" t="n">
-        <v>2.92</v>
+        <v>2.32</v>
       </c>
       <c r="U59" t="n">
-        <v>2.63</v>
+        <v>3.35</v>
       </c>
       <c r="V59" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="W59" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X59" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="Z59" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK59" t="n">
-        <v>2.3</v>
+        <v>1.51</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>46215.83333333334</v>
+        <v>46215.84027777778</v>
       </c>
     </row>
     <row r="60">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,64 +9947,64 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10050,165 +10050,6 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46215.84027777778</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>46215</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Real Tomayapo</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Independiente Petrolero</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU61" s="3" t="n">
         <v>46215.85416666666</v>
       </c>
     </row>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.04</v>
+        <v>2.61</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="P4" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.79</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.02</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="P6" t="n">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="P7" t="n">
-        <v>3.3</v>
+        <v>2.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="O8" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
         <v>2</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB8" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,65 +2633,65 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.53</v>
+        <v>4.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.99</v>
+        <v>6.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="S14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.25</v>
       </c>
-      <c r="T14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AF14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.48</v>
+        <v>2.71</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>3.29</v>
       </c>
       <c r="P15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="O16" t="n">
-        <v>3.29</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.6</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK16" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="O17" t="n">
-        <v>4.9</v>
+        <v>3.53</v>
       </c>
       <c r="P17" t="n">
-        <v>6.6</v>
+        <v>2.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.14</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.71</v>
+        <v>1.48</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O19" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="S19" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="T19" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC19" t="n">
         <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R20" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="S20" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U20" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.4</v>
       </c>
-      <c r="O25" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="P25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="AE25" t="n">
         <v>1.15</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK25" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,65 +4541,65 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="P26" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="R26" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S26" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="T26" t="n">
-        <v>3.15</v>
+        <v>3.66</v>
       </c>
       <c r="U26" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="V26" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG26" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="R27" t="n">
         <v>2.3</v>
       </c>
       <c r="S27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T27" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U27" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
         <v>4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="O33" t="n">
-        <v>5.2</v>
+        <v>6.55</v>
       </c>
       <c r="P33" t="n">
-        <v>6.11</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="R33" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S33" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="V33" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z33" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AB33" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.64</v>
+        <v>3.7</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,65 +5813,65 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="O34" t="n">
-        <v>6.55</v>
+        <v>3.56</v>
       </c>
       <c r="P34" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Q34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.53</v>
       </c>
-      <c r="R34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.53</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK34" t="n">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.5</v>
       </c>
-      <c r="O35" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="P35" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AD35" t="n">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>1</v>
+        <v>1.62</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.32</v>
+        <v>1.33</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="O37" t="n">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>3.49</v>
       </c>
       <c r="R37" t="n">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="S37" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="T37" t="n">
-        <v>2.18</v>
+        <v>2.73</v>
       </c>
       <c r="U37" t="n">
-        <v>3.58</v>
+        <v>2.56</v>
       </c>
       <c r="V37" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="W37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X37" t="n">
         <v>1.01</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Y37" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="O38" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="P38" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="R38" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="S38" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="T38" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="U38" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="V38" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE38" t="n">
         <v>1.01</v>
       </c>
-      <c r="X38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF38" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.78</v>
+        <v>2.26</v>
       </c>
       <c r="O41" t="n">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="P41" t="n">
-        <v>2.27</v>
+        <v>3.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.49</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="S41" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="T41" t="n">
-        <v>2.73</v>
+        <v>2.18</v>
       </c>
       <c r="U41" t="n">
-        <v>2.56</v>
+        <v>3.58</v>
       </c>
       <c r="V41" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="W41" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X41" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.5</v>
+        <v>2.32</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.91</v>
+        <v>3.96</v>
       </c>
       <c r="R42" t="n">
         <v>1.94</v>
       </c>
       <c r="S42" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T42" t="n">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="U42" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="V42" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
         <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="S43" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="T43" t="n">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="U43" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="V43" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.98</v>
+        <v>5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK43" t="n">
         <v>1.36</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,80 +7403,80 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U44" t="n">
         <v>3.2</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="R44" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.92</v>
-      </c>
       <c r="V44" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W44" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
         <v>1.04</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z44" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK44" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="O45" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="P45" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF45" t="n">
         <v>2.7</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,34 +7721,34 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="O46" t="n">
-        <v>3.32</v>
+        <v>2.72</v>
       </c>
       <c r="P46" t="n">
-        <v>5.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.15</v>
+        <v>3.06</v>
       </c>
       <c r="R46" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S46" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T46" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="U46" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="V46" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W46" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X46" t="n">
         <v>1.08</v>
@@ -7757,16 +7757,16 @@
         <v>1.57</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AC46" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AD46" t="n">
         <v>1.13</v>
@@ -7775,10 +7775,10 @@
         <v>1.03</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AC47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="O5" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="P5" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.54</v>
+        <v>2.86</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U6" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.86</v>
+        <v>2.54</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>1.96</v>
       </c>
       <c r="O14" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="P14" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="T14" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK14" t="n">
-        <v>2.71</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.29</v>
+        <v>4.9</v>
       </c>
       <c r="P15" t="n">
-        <v>3.29</v>
+        <v>6.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
-        <v>2.15</v>
+        <v>2.58</v>
       </c>
       <c r="S15" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="U15" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>2.21</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AF15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.08</v>
       </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.73</v>
+        <v>2.71</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>3.29</v>
       </c>
       <c r="P16" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="P19" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="S20" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="T20" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC20" t="n">
         <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3.04</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.9</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
-        <v>3.48</v>
+        <v>3.93</v>
       </c>
       <c r="P23" t="n">
-        <v>3.85</v>
+        <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.45</v>
+        <v>3.98</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="S23" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U23" t="n">
-        <v>2.84</v>
+        <v>2.22</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.12</v>
+        <v>2.33</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>1.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.93</v>
+        <v>3.48</v>
       </c>
       <c r="P24" t="n">
-        <v>1.63</v>
+        <v>3.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.98</v>
+        <v>2.45</v>
       </c>
       <c r="R24" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T24" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>2.22</v>
+        <v>2.84</v>
       </c>
       <c r="V24" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.33</v>
+        <v>3.12</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,80 +4541,80 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="O26" t="n">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="P26" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="R26" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="T26" t="n">
-        <v>3.66</v>
+        <v>3.15</v>
       </c>
       <c r="U26" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="V26" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.21</v>
+        <v>2.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="AK26" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>3</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,65 +4700,65 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="O27" t="n">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="P27" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="R27" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S27" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="T27" t="n">
-        <v>3.15</v>
+        <v>3.66</v>
       </c>
       <c r="U27" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AB27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG27" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="O33" t="n">
-        <v>6.55</v>
+        <v>5.2</v>
       </c>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>6.11</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="R33" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="T33" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="U33" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="V33" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z33" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK33" t="n">
-        <v>3.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="O35" t="n">
-        <v>5.2</v>
+        <v>6.55</v>
       </c>
       <c r="P35" t="n">
-        <v>6.11</v>
+        <v>7</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="R35" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S35" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="T35" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="V35" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z35" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AB35" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG35" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.64</v>
+        <v>3.7</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="O37" t="n">
-        <v>3.32</v>
+        <v>2.72</v>
       </c>
       <c r="P37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T37" t="n">
         <v>2.27</v>
       </c>
-      <c r="Q37" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.73</v>
-      </c>
       <c r="U37" t="n">
-        <v>2.56</v>
+        <v>3.68</v>
       </c>
       <c r="V37" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.78</v>
+        <v>2.7</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.88</v>
+        <v>5.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.23</v>
+        <v>3.16</v>
       </c>
       <c r="O38" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="P38" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.94</v>
+        <v>3.96</v>
       </c>
       <c r="R38" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="S38" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T38" t="n">
-        <v>2.31</v>
+        <v>2.59</v>
       </c>
       <c r="U38" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="V38" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.8</v>
+        <v>3.98</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P39" t="n">
-        <v>2.85</v>
+        <v>2.27</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.94</v>
+        <v>3.49</v>
       </c>
       <c r="R39" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="S39" t="n">
         <v>1.38</v>
       </c>
       <c r="T39" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="U39" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="V39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.32</v>
       </c>
-      <c r="W39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE39" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O41" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="P41" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="R41" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="S41" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="T41" t="n">
-        <v>2.18</v>
+        <v>2.67</v>
       </c>
       <c r="U41" t="n">
-        <v>3.58</v>
+        <v>2.92</v>
       </c>
       <c r="V41" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X41" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.32</v>
+        <v>3.08</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AE41" t="n">
         <v>1.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
         <v>2.91</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.96</v>
       </c>
       <c r="R42" t="n">
         <v>1.94</v>
       </c>
       <c r="S42" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T42" t="n">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="U42" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="V42" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
         <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AC43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7412,55 +7412,55 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.91</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="S44" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="T44" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="U44" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="V44" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W44" t="n">
         <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.37</v>
+        <v>3.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE44" t="n">
         <v>1.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,52 +7562,52 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.56</v>
+        <v>2.26</v>
       </c>
       <c r="O45" t="n">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="P45" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="R45" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S45" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T45" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U45" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="V45" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y45" t="n">
         <v>1.57</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB45" t="n">
         <v>1.4</v>
       </c>
       <c r="AC45" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AD45" t="n">
         <v>1.13</v>
@@ -7616,10 +7616,10 @@
         <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.18</v>
+        <v>1.52</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,34 +7721,34 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="O46" t="n">
-        <v>2.72</v>
+        <v>3.32</v>
       </c>
       <c r="P46" t="n">
-        <v>2.85</v>
+        <v>5.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.06</v>
+        <v>2.15</v>
       </c>
       <c r="R46" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S46" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="T46" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="U46" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="V46" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W46" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X46" t="n">
         <v>1.08</v>
@@ -7757,16 +7757,16 @@
         <v>1.57</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AD46" t="n">
         <v>1.13</v>
@@ -7775,10 +7775,10 @@
         <v>1.03</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="O53" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="P53" t="n">
-        <v>2.63</v>
+        <v>5.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="O54" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="P54" t="n">
-        <v>5.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AC54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="O2" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="Q2" t="n">
         <v>2.43</v>
@@ -740,19 +740,19 @@
         <v>2.43</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="U2" t="n">
         <v>2.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -761,28 +761,28 @@
         <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1043,55 +1043,55 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="O4" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S4" t="n">
         <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
         <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB4" t="n">
         <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
         <v>1.08</v>
@@ -1100,7 +1100,7 @@
         <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="O5" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
         <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1364,19 +1364,19 @@
         <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S6" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T6" t="n">
         <v>2.34</v>
@@ -1385,40 +1385,40 @@
         <v>3.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK6" t="n">
         <v>1.5</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="P8" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T11" t="n">
-        <v>3.01</v>
+        <v>2.79</v>
       </c>
       <c r="U11" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="V11" t="n">
         <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.52</v>
+        <v>1.97</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2483,37 +2483,37 @@
         <v>3.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
         <v>2.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.8</v>
+        <v>4.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB13" t="n">
         <v>2.3</v>
@@ -2531,7 +2531,7 @@
         <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4</v>
+        <v>2.89</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="O15" t="n">
-        <v>4.9</v>
+        <v>3.76</v>
       </c>
       <c r="P15" t="n">
-        <v>6.6</v>
+        <v>3.13</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.71</v>
+        <v>1.48</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.6</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK16" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,65 +3110,65 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.23</v>
+        <v>1.36</v>
       </c>
       <c r="O17" t="n">
-        <v>3.53</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.99</v>
+        <v>6.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AB17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.48</v>
+        <v>2.75</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3275,7 +3275,7 @@
         <v>4.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Q18" t="n">
         <v>5</v>
@@ -3284,13 +3284,13 @@
         <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T18" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V18" t="n">
         <v>1.67</v>
@@ -3302,7 +3302,7 @@
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
         <v>5.5</v>
@@ -3314,19 +3314,19 @@
         <v>2.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.55</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.31</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="P21" t="n">
-        <v>4.69</v>
+        <v>3.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.34</v>
+        <v>2.85</v>
       </c>
       <c r="R21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T21" t="n">
-        <v>2.47</v>
+        <v>2.68</v>
       </c>
       <c r="U21" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="V21" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
         <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="O22" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U22" t="n">
         <v>3.14</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.05</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
         <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>1.9</v>
       </c>
       <c r="O23" t="n">
-        <v>3.93</v>
+        <v>3.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.63</v>
+        <v>3.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.98</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T23" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.22</v>
+        <v>2.77</v>
       </c>
       <c r="V23" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.9</v>
+        <v>4.15</v>
       </c>
       <c r="O24" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="P24" t="n">
-        <v>3.85</v>
+        <v>1.71</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>2.84</v>
+        <v>2.15</v>
       </c>
       <c r="V24" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.12</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.78</v>
+        <v>1.15</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,43 +4382,43 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P25" t="n">
-        <v>3.15</v>
+        <v>4.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R25" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.3</v>
       </c>
-      <c r="S25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.52</v>
-      </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA25" t="n">
         <v>1.67</v>
@@ -4427,7 +4427,7 @@
         <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="AD25" t="n">
         <v>1.4</v>
@@ -4436,10 +4436,10 @@
         <v>1.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="P26" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="R26" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S26" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T26" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="V26" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
-        <v>5.05</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="S27" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T27" t="n">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.05</v>
+        <v>4.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.21</v>
+        <v>2.63</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AK27" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4865,19 +4865,19 @@
         <v>3.45</v>
       </c>
       <c r="P28" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="R28" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U28" t="n">
         <v>2.43</v>
@@ -4886,28 +4886,28 @@
         <v>1.43</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE28" t="n">
         <v>1.12</v>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5345,46 +5345,46 @@
         <v>1.78</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T31" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U31" t="n">
         <v>2.2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W31" t="n">
         <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE31" t="n">
         <v>1.22</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AK31" t="n">
         <v>1.25</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.42</v>
+        <v>1.33</v>
       </c>
       <c r="O32" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>4.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.96</v>
+        <v>1.75</v>
       </c>
       <c r="R32" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="S32" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="T32" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="U32" t="n">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="V32" t="n">
-        <v>1.74</v>
+        <v>2.14</v>
       </c>
       <c r="W32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA32" t="n">
         <v>1.16</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AB32" t="n">
-        <v>2.62</v>
+        <v>4.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.01</v>
+        <v>1.53</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.78</v>
+        <v>2.45</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,80 +5654,80 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="O33" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>6.11</v>
+        <v>5.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="R33" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="S33" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>2.41</v>
       </c>
       <c r="U33" t="n">
-        <v>1.66</v>
+        <v>3.2</v>
       </c>
       <c r="V33" t="n">
-        <v>2.14</v>
+        <v>1.26</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AF33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.05</v>
       </c>
-      <c r="Z33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AK33" t="n">
-        <v>2.64</v>
+        <v>2.12</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>3.56</v>
+        <v>3.82</v>
       </c>
       <c r="P34" t="n">
-        <v>6.7</v>
+        <v>2.35</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.23</v>
+        <v>2.96</v>
       </c>
       <c r="R34" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="T34" t="n">
-        <v>2.41</v>
+        <v>4.05</v>
       </c>
       <c r="U34" t="n">
-        <v>3.25</v>
+        <v>2.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.29</v>
+        <v>1.74</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="X34" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.46</v>
+        <v>1.11</v>
       </c>
       <c r="Z34" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB34" t="n">
         <v>2.63</v>
       </c>
-      <c r="AA34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC34" t="n">
-        <v>4.33</v>
+        <v>2.01</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AE34" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.32</v>
+        <v>1.34</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.53</v>
+        <v>2.99</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5975,31 +5975,31 @@
         <v>1.19</v>
       </c>
       <c r="O35" t="n">
-        <v>6.55</v>
+        <v>6.7</v>
       </c>
       <c r="P35" t="n">
-        <v>7</v>
+        <v>8.35</v>
       </c>
       <c r="Q35" t="n">
         <v>1.53</v>
       </c>
       <c r="R35" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="S35" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="T35" t="n">
         <v>5.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V35" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
@@ -6011,16 +6011,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AB35" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AE35" t="n">
         <v>1.53</v>
@@ -6029,7 +6029,7 @@
         <v>1.44</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK35" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="O37" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="P37" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>2.7</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AC37" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>3.16</v>
+        <v>2.23</v>
       </c>
       <c r="O38" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="P38" t="n">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.96</v>
+        <v>2.7</v>
       </c>
       <c r="R38" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="S38" t="n">
         <v>1.49</v>
       </c>
       <c r="T38" t="n">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="U38" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="V38" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE38" t="n">
         <v>1.01</v>
       </c>
-      <c r="X38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="AF38" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK38" t="n">
         <v>1.61</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6617,55 +6617,55 @@
         <v>2.27</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S39" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T39" t="n">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="U39" t="n">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="V39" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W39" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
         <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK39" t="n">
         <v>1.36</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,80 +6767,80 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="O40" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="P40" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="R40" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="S40" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="T40" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="U40" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="V40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.24</v>
       </c>
-      <c r="W40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK40" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.28</v>
+        <v>3.16</v>
       </c>
       <c r="O41" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="P41" t="n">
-        <v>2.85</v>
+        <v>2.42</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.94</v>
+        <v>3.71</v>
       </c>
       <c r="R41" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="T41" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="U41" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="V41" t="n">
         <v>1.32</v>
       </c>
       <c r="W41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE41" t="n">
         <v>1.06</v>
       </c>
-      <c r="X41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF41" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7094,55 +7094,55 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="O43" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="P43" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="R44" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="S44" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="T44" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U44" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="V44" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE44" t="n">
         <v>1.03</v>
       </c>
-      <c r="X44" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF44" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,55 +7562,55 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O45" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
         <v>3.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S45" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="T45" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="U45" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="V45" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AC45" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE45" t="n">
         <v>1.03</v>
@@ -7619,7 +7619,7 @@
         <v>2.15</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="R46" t="n">
         <v>1.95</v>
       </c>
       <c r="S46" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="T46" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="U46" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="V46" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W46" t="n">
         <v>1.04</v>
       </c>
       <c r="X46" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB46" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AC46" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE46" t="n">
         <v>1.03</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7889,55 +7889,55 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q48" t="n">
         <v>3.2</v>
       </c>
-      <c r="P48" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R48" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T48" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="V48" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W48" t="n">
         <v>1.06</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z48" t="n">
         <v>2.9</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB48" t="n">
         <v>1.66</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="AD48" t="n">
         <v>1.22</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF48" t="n">
         <v>1.83</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK48" t="n">
         <v>1.4</v>
@@ -8198,25 +8198,25 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P49" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R49" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S49" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T49" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="U49" t="n">
         <v>3.76</v>
@@ -8228,13 +8228,13 @@
         <v>1.01</v>
       </c>
       <c r="X49" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AA49" t="n">
         <v>2.59</v>
@@ -8243,19 +8243,19 @@
         <v>1.44</v>
       </c>
       <c r="AC49" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF49" t="n">
         <v>2.18</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8366,7 +8366,7 @@
         <v>2.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
         <v>2.15</v>
@@ -8375,10 +8375,10 @@
         <v>1.34</v>
       </c>
       <c r="T50" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="U50" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V50" t="n">
         <v>1.36</v>
@@ -8387,34 +8387,34 @@
         <v>1.06</v>
       </c>
       <c r="X50" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AD50" t="n">
         <v>1.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF50" t="n">
         <v>1.73</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8516,55 +8516,55 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
         <v>2.6</v>
       </c>
       <c r="P51" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
         <v>1.83</v>
       </c>
       <c r="S51" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="T51" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U51" t="n">
         <v>4</v>
       </c>
       <c r="V51" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W51" t="n">
         <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE51" t="n">
         <v>1.02</v>
@@ -8573,7 +8573,7 @@
         <v>2.2</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AK51" t="n">
         <v>1.44</v>
@@ -8684,55 +8684,55 @@
         <v>2.27</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="R52" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="S52" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T52" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="U52" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V52" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W52" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X52" t="n">
         <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z52" t="n">
-        <v>6.07</v>
+        <v>5.65</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AF52" t="n">
         <v>1.36</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AK52" t="n">
         <v>1.44</v>
@@ -8837,25 +8837,25 @@
         <v>1.61</v>
       </c>
       <c r="O53" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P53" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="R53" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="S53" t="n">
         <v>1.6</v>
       </c>
       <c r="T53" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U53" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="V53" t="n">
         <v>1.2</v>
@@ -8864,22 +8864,22 @@
         <v>1.01</v>
       </c>
       <c r="X53" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AB53" t="n">
         <v>1.4</v>
       </c>
       <c r="AC53" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AD53" t="n">
         <v>1.13</v>
@@ -8888,7 +8888,7 @@
         <v>1.03</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.23</v>
+        <v>2.57</v>
       </c>
       <c r="AG53" t="n">
         <v>1.44</v>
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="O54" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P54" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9320,49 +9320,49 @@
         <v>3.79</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R56" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S56" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T56" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="U56" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="V56" t="n">
         <v>1.39</v>
       </c>
       <c r="W56" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X56" t="n">
         <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z56" t="n">
         <v>3.28</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD56" t="n">
         <v>1.27</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF56" t="n">
         <v>1.75</v>
@@ -9384,7 +9384,7 @@
         <v>1.19</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9470,34 +9470,34 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="O57" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="P57" t="n">
-        <v>4.74</v>
+        <v>4.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="R57" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="S57" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T57" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U57" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="V57" t="n">
         <v>1.3</v>
       </c>
       <c r="W57" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X57" t="n">
         <v>1.03</v>
@@ -9506,28 +9506,28 @@
         <v>1.36</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AB57" t="n">
         <v>1.64</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF57" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9641,22 +9641,22 @@
         <v>2</v>
       </c>
       <c r="R58" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S58" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T58" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="U58" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="V58" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W58" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X58" t="n">
         <v>1.04</v>
@@ -9668,19 +9668,19 @@
         <v>3.5</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD58" t="n">
         <v>1.3</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF58" t="n">
         <v>1.85</v>
@@ -9702,7 +9702,7 @@
         <v>1.25</v>
       </c>
       <c r="AK58" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9794,58 +9794,58 @@
         <v>2.99</v>
       </c>
       <c r="P59" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="R59" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="S59" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="T59" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="U59" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="V59" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W59" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X59" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y59" t="n">
         <v>1.44</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AC59" t="n">
-        <v>4.75</v>
+        <v>6.33</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE59" t="n">
         <v>1.01</v>
       </c>
       <c r="AF59" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.62</v>
+        <v>4.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.03</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.1</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.32</v>
+        <v>1.72</v>
       </c>
       <c r="O19" t="n">
         <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="O20" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="P22" t="n">
-        <v>4.7</v>
+        <v>3.51</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.9</v>
+        <v>4.15</v>
       </c>
       <c r="O23" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P23" t="n">
-        <v>3.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U23" t="n">
         <v>2.15</v>
       </c>
-      <c r="S23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.77</v>
-      </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.78</v>
+        <v>1.15</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.15</v>
+        <v>1.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>2.15</v>
+        <v>2.77</v>
       </c>
       <c r="V24" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.33</v>
       </c>
-      <c r="O32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="T32" t="n">
-        <v>5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V32" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,80 +5813,80 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="O34" t="n">
-        <v>3.82</v>
+        <v>5.2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.35</v>
+        <v>4.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.96</v>
+        <v>1.75</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="T34" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="U34" t="n">
-        <v>2.01</v>
+        <v>1.55</v>
       </c>
       <c r="V34" t="n">
-        <v>1.74</v>
+        <v>2.14</v>
       </c>
       <c r="W34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA34" t="n">
         <v>1.16</v>
       </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="AB34" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z34" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK34" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="O37" t="n">
         <v>2.85</v>
       </c>
       <c r="P37" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.78</v>
+        <v>1.92</v>
       </c>
       <c r="O39" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="P39" t="n">
-        <v>2.27</v>
+        <v>3.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.28</v>
+        <v>3.16</v>
       </c>
       <c r="O40" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="P40" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.78</v>
+        <v>3.71</v>
       </c>
       <c r="R40" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="T40" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U40" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X40" t="n">
         <v>1.08</v>
       </c>
-      <c r="X40" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y40" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.28</v>
+        <v>3.85</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,31 +6926,31 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.16</v>
+        <v>1.55</v>
       </c>
       <c r="O41" t="n">
-        <v>2.91</v>
+        <v>3.35</v>
       </c>
       <c r="P41" t="n">
-        <v>2.42</v>
+        <v>5.7</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.71</v>
+        <v>2.15</v>
       </c>
       <c r="R41" t="n">
         <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="T41" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V41" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="W41" t="n">
         <v>1.03</v>
@@ -6959,31 +6959,31 @@
         <v>1.08</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.85</v>
+        <v>5.68</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.81</v>
+        <v>1.41</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S43" t="n">
         <v>1.55</v>
       </c>
-      <c r="O43" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P43" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R43" t="n">
-        <v>2</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.53</v>
-      </c>
       <c r="T43" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U43" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V43" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X43" t="n">
         <v>1.08</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AC43" t="n">
-        <v>5.68</v>
+        <v>6</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE43" t="n">
         <v>1.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P44" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="R44" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="S44" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="T44" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="U44" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="V44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD44" t="n">
         <v>1.25</v>
       </c>
-      <c r="W44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>1.24</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R45" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="S45" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T45" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="U45" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="V45" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W45" t="n">
         <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AC45" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE45" t="n">
         <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7730,55 +7730,55 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="R46" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S46" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="T46" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="U46" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="V46" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="W46" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.05</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.17</v>
       </c>
       <c r="AE46" t="n">
         <v>1.03</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK46" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z47" t="n">
         <v>3.6</v>
       </c>
-      <c r="R47" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S47" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U47" t="n">
-        <v>4</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AA47" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AC47" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.61</v>
+        <v>2.24</v>
       </c>
       <c r="O53" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P53" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AC53" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.24</v>
+        <v>1.61</v>
       </c>
       <c r="O54" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="P54" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="O4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3.05</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.25</v>
+        <v>3.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.42</v>
+        <v>2.76</v>
       </c>
       <c r="R7" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T7" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U7" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.02</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="T8" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,55 +2006,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
         <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4</v>
+        <v>6.55</v>
       </c>
       <c r="Q14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R14" t="n">
         <v>2.6</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S14" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>2.89</v>
+        <v>2.07</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>2.48</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="O15" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="Q15" t="n">
         <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.25</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="P16" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R16" t="n">
         <v>2.4</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.23</v>
-      </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB16" t="n">
         <v>2.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="n">
         <v>1.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>6.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.6</v>
       </c>
-      <c r="S17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
         <v>2.1</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="P19" t="n">
-        <v>4.7</v>
+        <v>3.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="R19" t="n">
         <v>2</v>
@@ -3446,46 +3446,46 @@
         <v>1.46</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="U19" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
         <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,16 +3746,16 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="O21" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>3.14</v>
+        <v>4.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="R21" t="n">
         <v>2</v>
@@ -3764,46 +3764,46 @@
         <v>1.46</v>
       </c>
       <c r="T21" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
         <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O33" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="P33" t="n">
-        <v>5.75</v>
+        <v>4.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="R33" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="T33" t="n">
-        <v>2.41</v>
+        <v>5</v>
       </c>
       <c r="U33" t="n">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>1.26</v>
+        <v>2.14</v>
       </c>
       <c r="W33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X33" t="n">
         <v>1</v>
       </c>
-      <c r="X33" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.65</v>
+        <v>10</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.23</v>
+        <v>1.16</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.55</v>
+        <v>4.25</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.33</v>
+        <v>1.53</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.14</v>
+        <v>2.45</v>
       </c>
       <c r="AE33" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.57</v>
+        <v>3.04</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="O34" t="n">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="P34" t="n">
-        <v>4.65</v>
+        <v>8.35</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="R34" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="S34" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="V34" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="W34" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X34" t="n">
         <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Z34" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AB34" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AC34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AF34" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.04</v>
+        <v>2.49</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>1.11</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="O35" t="n">
-        <v>6.7</v>
+        <v>3.6</v>
       </c>
       <c r="P35" t="n">
-        <v>8.35</v>
+        <v>5.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="R35" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="S35" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="T35" t="n">
-        <v>5.5</v>
+        <v>2.41</v>
       </c>
       <c r="U35" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="V35" t="n">
-        <v>2.06</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1</v>
       </c>
-      <c r="Y35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF35" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.49</v>
+        <v>1.57</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK35" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="S37" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="T37" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="U37" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="W37" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AE37" t="n">
         <v>1.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="O39" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="P39" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.16</v>
+        <v>2.26</v>
       </c>
       <c r="O40" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="P40" t="n">
-        <v>2.42</v>
+        <v>3.38</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.71</v>
+        <v>3.04</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S40" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="T40" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="U40" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="V40" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="W40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE40" t="n">
         <v>1.03</v>
       </c>
-      <c r="X40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S41" t="n">
         <v>1.55</v>
       </c>
-      <c r="O41" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P41" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R41" t="n">
-        <v>2</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1.53</v>
-      </c>
       <c r="T41" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V41" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X41" t="n">
         <v>1.08</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.68</v>
+        <v>6</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE41" t="n">
         <v>1.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="O42" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="P42" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="R42" t="n">
         <v>2.06</v>
       </c>
       <c r="S42" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="T42" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="U42" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="V42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.25</v>
       </c>
-      <c r="W42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AE42" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,61 +7403,61 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="O44" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P44" t="n">
-        <v>3.05</v>
+        <v>2.27</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="R44" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S44" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V44" t="n">
         <v>1.35</v>
       </c>
-      <c r="T44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.4</v>
-      </c>
       <c r="W44" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
         <v>1.3</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA44" t="n">
         <v>1.92</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG44" t="n">
         <v>1.95</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R45" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="S45" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T45" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="U45" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="V45" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="R46" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="S46" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="T46" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="U46" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="V46" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="W46" t="n">
         <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R47" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S47" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T47" t="n">
-        <v>2.64</v>
+        <v>2.41</v>
       </c>
       <c r="U47" t="n">
-        <v>2.79</v>
+        <v>3.4</v>
       </c>
       <c r="V47" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W47" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R50" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="S50" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="T50" t="n">
-        <v>2.82</v>
+        <v>2.11</v>
       </c>
       <c r="U50" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="W50" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.76</v>
+        <v>3.2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.79</v>
+        <v>1.32</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.28</v>
+        <v>6.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O51" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="P51" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="S51" t="n">
-        <v>1.71</v>
+        <v>1.34</v>
       </c>
       <c r="T51" t="n">
-        <v>2.11</v>
+        <v>2.82</v>
       </c>
       <c r="U51" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="V51" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="W51" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X51" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8837,10 +8837,10 @@
         <v>2.24</v>
       </c>
       <c r="O53" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P53" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>2.99</v>
       </c>
       <c r="P59" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="Q59" t="n">
         <v>2.8</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.73</v>
+        <v>1.96</v>
       </c>
       <c r="O4" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
         <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.03</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.1</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,55 +2006,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
         <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,55 +2165,55 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,61 +2633,61 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>6.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.6</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG14" t="n">
         <v>2.1</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.45</v>
+        <v>6.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.1</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z17" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
         <v>2.1</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,28 +3428,28 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O19" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T19" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V19" t="n">
         <v>1.33</v>
@@ -3458,34 +3458,34 @@
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="P22" t="n">
-        <v>3.51</v>
+        <v>3.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.15</v>
+        <v>1.9</v>
       </c>
       <c r="O23" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T23" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.15</v>
+        <v>2.77</v>
       </c>
       <c r="V23" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.9</v>
+        <v>4.15</v>
       </c>
       <c r="O24" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U24" t="n">
         <v>2.15</v>
       </c>
-      <c r="S24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.77</v>
-      </c>
       <c r="V24" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.78</v>
+        <v>1.15</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="P25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.62</v>
       </c>
-      <c r="O25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P25" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AG25" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,65 +4541,65 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="O26" t="n">
-        <v>5.05</v>
+        <v>3.6</v>
       </c>
       <c r="P26" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="S26" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U26" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AC26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG26" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P27" t="n">
-        <v>3.4</v>
+        <v>4.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="R27" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="S27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T27" t="n">
         <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD27" t="n">
         <v>1.4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O32" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>2.35</v>
+        <v>5.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.96</v>
+        <v>2.1</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S32" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="T32" t="n">
-        <v>4.05</v>
+        <v>2.41</v>
       </c>
       <c r="U32" t="n">
-        <v>2.01</v>
+        <v>3.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.74</v>
+        <v>1.26</v>
       </c>
       <c r="W32" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.22</v>
+        <v>2.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.38</v>
+        <v>2.23</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.01</v>
+        <v>4.33</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.99</v>
+        <v>1.57</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1.33</v>
       </c>
-      <c r="O33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P33" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="T33" t="n">
-        <v>5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V33" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AF33" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O35" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="P35" t="n">
-        <v>5.75</v>
+        <v>4.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="R35" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="S35" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="T35" t="n">
-        <v>2.41</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>2.14</v>
       </c>
       <c r="W35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X35" t="n">
         <v>1</v>
       </c>
-      <c r="X35" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y35" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.65</v>
+        <v>10</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.23</v>
+        <v>1.16</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>4.25</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.33</v>
+        <v>1.53</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.14</v>
+        <v>2.45</v>
       </c>
       <c r="AE35" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.57</v>
+        <v>3.04</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6299,55 +6299,55 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S37" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="T37" t="n">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="V37" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AC37" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AE37" t="n">
         <v>1.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.55</v>
+        <v>2.78</v>
       </c>
       <c r="O39" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P39" t="n">
-        <v>5.7</v>
+        <v>2.27</v>
       </c>
       <c r="Q39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R39" t="n">
         <v>2.15</v>
       </c>
-      <c r="R39" t="n">
-        <v>2</v>
-      </c>
       <c r="S39" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="U39" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z39" t="n">
         <v>3.6</v>
       </c>
-      <c r="V39" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AA39" t="n">
-        <v>2.62</v>
+        <v>1.92</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.68</v>
+        <v>3.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O40" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="P40" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R40" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="S40" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="T40" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U40" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="V40" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W40" t="n">
         <v>1.04</v>
       </c>
       <c r="X40" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.7</v>
+        <v>5.86</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF40" t="n">
         <v>2.15</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK40" t="n">
         <v>1.57</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,80 +6926,80 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="O41" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="P41" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R41" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="S41" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="T41" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA41" t="n">
         <v>2.3</v>
       </c>
-      <c r="U41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V41" t="n">
+      <c r="AB41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
         <v>1.23</v>
       </c>
-      <c r="W41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AK41" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="S42" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="T42" t="n">
-        <v>2.9</v>
+        <v>2.04</v>
       </c>
       <c r="U42" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="W42" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE42" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.78</v>
+        <v>1.92</v>
       </c>
       <c r="O44" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="P44" t="n">
-        <v>2.27</v>
+        <v>3.9</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="O45" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="P45" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="R45" t="n">
         <v>2.06</v>
       </c>
       <c r="S45" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="T45" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="U45" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="V45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.25</v>
       </c>
-      <c r="W45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AE45" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.16</v>
+        <v>2.26</v>
       </c>
       <c r="O46" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="P46" t="n">
-        <v>2.42</v>
+        <v>3.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.71</v>
+        <v>3.04</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S46" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="T46" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="U46" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="V46" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="W46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE46" t="n">
         <v>1.03</v>
       </c>
-      <c r="X46" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF46" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="R47" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S47" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T47" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="U47" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V47" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="W47" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB47" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC47" t="n">
-        <v>4.1</v>
+        <v>5.68</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AE47" t="n">
         <v>1.03</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.93</v>
+        <v>2.67</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.53</v>
+        <v>2.18</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="S50" t="n">
-        <v>1.71</v>
+        <v>1.34</v>
       </c>
       <c r="T50" t="n">
-        <v>2.11</v>
+        <v>2.82</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="V50" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="W50" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X50" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="AC50" t="n">
-        <v>6.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="P51" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R51" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="S51" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="T51" t="n">
-        <v>2.82</v>
+        <v>2.11</v>
       </c>
       <c r="U51" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="V51" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="W51" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.76</v>
+        <v>3.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.79</v>
+        <v>1.32</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.28</v>
+        <v>6.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.24</v>
+        <v>1.61</v>
       </c>
       <c r="O53" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="P53" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.61</v>
+        <v>2.24</v>
       </c>
       <c r="O54" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="P54" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AC54" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9341,25 +9341,25 @@
         <v>1.08</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y56" t="n">
         <v>1.28</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC56" t="n">
         <v>3.3</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE56" t="n">
         <v>1.1</v>

--- a/jogos_2026-07-12.xlsx
+++ b/jogos_2026-07-12.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
         <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
         <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.24</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,55 +2006,55 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2.24</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
         <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.89</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AC10" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="P15" t="n">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="Q15" t="n">
         <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="U15" t="n">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="Q16" t="n">
         <v>2.6</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.25</v>
       </c>
-      <c r="T16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,28 +3428,28 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="P19" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="R19" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U19" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="V19" t="n">
         <v>1.33</v>
@@ -3458,34 +3458,34 @@
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.16</v>
+        <v>1.72</v>
       </c>
       <c r="O20" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>3.51</v>
+        <v>4.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="P21" t="n">
-        <v>4.7</v>
+        <v>3.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,28 +3905,28 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O22" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S22" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T22" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V22" t="n">
         <v>1.33</v>
@@ -3935,34 +3935,34 @@
         <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.9</v>
+        <v>4.15</v>
       </c>
       <c r="O23" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P23" t="n">
-        <v>3.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U23" t="n">
         <v>2.15</v>
       </c>
-      <c r="S23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.77</v>
-      </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.78</v>
+        <v>1.15</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.15</v>
+        <v>1.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.71</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>2.15</v>
+        <v>2.77</v>
       </c>
       <c r="V24" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.15</v>
+        <v>1.78</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,65 +4382,65 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="O25" t="n">
-        <v>5.05</v>
+        <v>3.6</v>
       </c>
       <c r="P25" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U25" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="AC25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG25" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="O26" t="n">
-        <v>3.6</v>
+        <v>5.05</v>
       </c>
       <c r="P26" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="R26" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T26" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z26" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF26" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4865,10 +4865,10 @@
         <v>3.45</v>
       </c>
       <c r="P28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="R28" t="n">
         <v>2.14</v>
@@ -4880,10 +4880,10 @@
         <v>2.97</v>
       </c>
       <c r="U28" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="V28" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W28" t="n">
         <v>1.09</v>
@@ -4892,25 +4892,25 @@
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
         <v>1.31</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF28" t="n">
         <v>1.66</v>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O32" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="P32" t="n">
-        <v>5.75</v>
+        <v>4.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="R32" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="S32" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="T32" t="n">
-        <v>2.41</v>
+        <v>5</v>
       </c>
       <c r="U32" t="n">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="V32" t="n">
-        <v>1.26</v>
+        <v>2.14</v>
       </c>
       <c r="W32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X32" t="n">
         <v>1</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.65</v>
+        <v>10</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.23</v>
+        <v>1.16</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.55</v>
+        <v>4.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.33</v>
+        <v>1.53</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.14</v>
+        <v>2.45</v>
       </c>
       <c r="AE32" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.57</v>
+        <v>3.04</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O33" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.35</v>
+        <v>5.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.96</v>
+        <v>2.1</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S33" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="T33" t="n">
-        <v>4.05</v>
+        <v>2.41</v>
       </c>
       <c r="U33" t="n">
-        <v>2.01</v>
+        <v>3.2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.74</v>
+        <v>1.26</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.22</v>
+        <v>2.65</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.38</v>
+        <v>2.23</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.01</v>
+        <v>4.33</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.99</v>
+        <v>1.57</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1.33</v>
       </c>
-      <c r="O35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P35" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="T35" t="n">
-        <v>5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V35" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AF35" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,65 +6290,65 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG37" t="n">
         <v>1.95</v>
       </c>
-      <c r="S37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R39" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S39" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T39" t="n">
-        <v>2.64</v>
+        <v>2.41</v>
       </c>
       <c r="U39" t="n">
-        <v>2.79</v>
+        <v>3.4</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="O40" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P40" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="R40" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="S40" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="T40" t="n">
-        <v>2.28</v>
+        <v>2.9</v>
       </c>
       <c r="U40" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="V40" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="W40" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X40" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.59</v>
+        <v>1.92</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="AC40" t="n">
-        <v>5.86</v>
+        <v>3.28</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="O41" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="P41" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
         <v>2.7</v>
       </c>
-      <c r="R41" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U41" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y41" t="n">
+      <c r="AB41" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z41" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AC41" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>